--- a/data/processed/harmonization/Major_and_trace_elements_total__Total_aluminum/harmonized.xlsx
+++ b/data/processed/harmonization/Major_and_trace_elements_total__Total_aluminum/harmonized.xlsx
@@ -432,7 +432,7 @@
     <col width="30" customWidth="1" min="1" max="1"/>
     <col width="58" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="17" customWidth="1" min="4" max="4"/>
+    <col width="23" customWidth="1" min="4" max="4"/>
     <col width="11" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="48" customWidth="1" min="7" max="7"/>
@@ -7774,12 +7774,12 @@
       </c>
       <c r="C152" s="2" t="inlineStr">
         <is>
-          <t>4:20-29</t>
+          <t>Hu:4:20-29</t>
         </is>
       </c>
       <c r="D152" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E152" s="2" t="inlineStr">
@@ -7809,7 +7809,7 @@
       <c r="K152" s="2" t="inlineStr"/>
       <c r="L152" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -7826,12 +7826,12 @@
       </c>
       <c r="C153" s="2" t="inlineStr">
         <is>
-          <t>4:10-20</t>
+          <t>Hu:4:10-20</t>
         </is>
       </c>
       <c r="D153" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E153" s="2" t="inlineStr">
@@ -7861,7 +7861,7 @@
       <c r="K153" s="2" t="inlineStr"/>
       <c r="L153" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -7878,12 +7878,12 @@
       </c>
       <c r="C154" s="2" t="inlineStr">
         <is>
-          <t>4:0-10</t>
+          <t>Hu:4:0-10</t>
         </is>
       </c>
       <c r="D154" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E154" s="2" t="inlineStr">
@@ -7913,7 +7913,7 @@
       <c r="K154" s="2" t="inlineStr"/>
       <c r="L154" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -7930,12 +7930,12 @@
       </c>
       <c r="C155" s="2" t="inlineStr">
         <is>
-          <t>4:-10-0</t>
+          <t>Ho:4:-10-0</t>
         </is>
       </c>
       <c r="D155" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E155" s="2" t="inlineStr">
@@ -7965,7 +7965,7 @@
       <c r="K155" s="2" t="inlineStr"/>
       <c r="L155" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -7982,12 +7982,12 @@
       </c>
       <c r="C156" s="2" t="inlineStr">
         <is>
-          <t>4:-20--10</t>
+          <t>Ho:4:-20--10</t>
         </is>
       </c>
       <c r="D156" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E156" s="2" t="inlineStr">
@@ -8017,7 +8017,7 @@
       <c r="K156" s="2" t="inlineStr"/>
       <c r="L156" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -8034,12 +8034,12 @@
       </c>
       <c r="C157" s="2" t="inlineStr">
         <is>
-          <t>4:-30--20</t>
+          <t>Ho:4:-30--20</t>
         </is>
       </c>
       <c r="D157" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E157" s="2" t="inlineStr">
@@ -8069,7 +8069,7 @@
       <c r="K157" s="2" t="inlineStr"/>
       <c r="L157" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -8086,12 +8086,12 @@
       </c>
       <c r="C158" s="2" t="inlineStr">
         <is>
-          <t>4:-40--30</t>
+          <t>Ho:4:-40--30</t>
         </is>
       </c>
       <c r="D158" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E158" s="2" t="inlineStr">
@@ -8121,7 +8121,7 @@
       <c r="K158" s="2" t="inlineStr"/>
       <c r="L158" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -8138,12 +8138,12 @@
       </c>
       <c r="C159" s="2" t="inlineStr">
         <is>
-          <t>4:-50--40</t>
+          <t>Ho:4:-50--40</t>
         </is>
       </c>
       <c r="D159" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E159" s="2" t="inlineStr">
@@ -8173,7 +8173,7 @@
       <c r="K159" s="2" t="inlineStr"/>
       <c r="L159" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -8190,12 +8190,12 @@
       </c>
       <c r="C160" s="2" t="inlineStr">
         <is>
-          <t>4:-60--50</t>
+          <t>Ho:4:-60--50</t>
         </is>
       </c>
       <c r="D160" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E160" s="2" t="inlineStr">
@@ -8225,7 +8225,7 @@
       <c r="K160" s="2" t="inlineStr"/>
       <c r="L160" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -8242,12 +8242,12 @@
       </c>
       <c r="C161" s="2" t="inlineStr">
         <is>
-          <t>4:-70--60</t>
+          <t>Ho:4:-70--60</t>
         </is>
       </c>
       <c r="D161" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E161" s="2" t="inlineStr">
@@ -8277,7 +8277,7 @@
       <c r="K161" s="2" t="inlineStr"/>
       <c r="L161" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -8294,12 +8294,12 @@
       </c>
       <c r="C162" s="2" t="inlineStr">
         <is>
-          <t>4:-80--70</t>
+          <t>Ho:4:-80--70</t>
         </is>
       </c>
       <c r="D162" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E162" s="2" t="inlineStr">
@@ -8329,7 +8329,7 @@
       <c r="K162" s="2" t="inlineStr"/>
       <c r="L162" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -8346,12 +8346,12 @@
       </c>
       <c r="C163" s="2" t="inlineStr">
         <is>
-          <t>4:-90--80</t>
+          <t>Ho:4:-90--80</t>
         </is>
       </c>
       <c r="D163" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E163" s="2" t="inlineStr">
@@ -8381,7 +8381,7 @@
       <c r="K163" s="2" t="inlineStr"/>
       <c r="L163" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -8398,12 +8398,12 @@
       </c>
       <c r="C164" s="2" t="inlineStr">
         <is>
-          <t>4:-100--90</t>
+          <t>Ho:4:-100--90</t>
         </is>
       </c>
       <c r="D164" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E164" s="2" t="inlineStr">
@@ -8433,7 +8433,7 @@
       <c r="K164" s="2" t="inlineStr"/>
       <c r="L164" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -8450,12 +8450,12 @@
       </c>
       <c r="C165" s="2" t="inlineStr">
         <is>
-          <t>4:-125--100</t>
+          <t>Ho:4:-125--100</t>
         </is>
       </c>
       <c r="D165" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E165" s="2" t="inlineStr">
@@ -8485,7 +8485,7 @@
       <c r="K165" s="2" t="inlineStr"/>
       <c r="L165" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -8502,12 +8502,12 @@
       </c>
       <c r="C166" s="2" t="inlineStr">
         <is>
-          <t>4:-150--125</t>
+          <t>Ho:4:-150--125</t>
         </is>
       </c>
       <c r="D166" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E166" s="2" t="inlineStr">
@@ -8537,7 +8537,7 @@
       <c r="K166" s="2" t="inlineStr"/>
       <c r="L166" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -8554,12 +8554,12 @@
       </c>
       <c r="C167" s="2" t="inlineStr">
         <is>
-          <t>4:-175--150</t>
+          <t>Ho:4:-175--150</t>
         </is>
       </c>
       <c r="D167" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E167" s="2" t="inlineStr">
@@ -8589,7 +8589,7 @@
       <c r="K167" s="2" t="inlineStr"/>
       <c r="L167" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -8606,12 +8606,12 @@
       </c>
       <c r="C168" s="2" t="inlineStr">
         <is>
-          <t>4:-200--175</t>
+          <t>Ho:4:-200--175</t>
         </is>
       </c>
       <c r="D168" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E168" s="2" t="inlineStr">
@@ -8641,7 +8641,7 @@
       <c r="K168" s="2" t="inlineStr"/>
       <c r="L168" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -8658,12 +8658,12 @@
       </c>
       <c r="C169" s="2" t="inlineStr">
         <is>
-          <t>4:-250--200</t>
+          <t>Ho:4:-250--200</t>
         </is>
       </c>
       <c r="D169" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E169" s="2" t="inlineStr">
@@ -8693,7 +8693,7 @@
       <c r="K169" s="2" t="inlineStr"/>
       <c r="L169" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -8710,12 +8710,12 @@
       </c>
       <c r="C170" s="2" t="inlineStr">
         <is>
-          <t>5:0-24</t>
+          <t>Hu:5:0-24</t>
         </is>
       </c>
       <c r="D170" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E170" s="2" t="inlineStr">
@@ -8745,7 +8745,7 @@
       <c r="K170" s="2" t="inlineStr"/>
       <c r="L170" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -8762,12 +8762,12 @@
       </c>
       <c r="C171" s="2" t="inlineStr">
         <is>
-          <t>5:10-18</t>
+          <t>Hu:5:10-18</t>
         </is>
       </c>
       <c r="D171" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E171" s="2" t="inlineStr">
@@ -8797,7 +8797,7 @@
       <c r="K171" s="2" t="inlineStr"/>
       <c r="L171" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -8814,12 +8814,12 @@
       </c>
       <c r="C172" s="2" t="inlineStr">
         <is>
-          <t>5:0-10</t>
+          <t>Hu:5:0-10</t>
         </is>
       </c>
       <c r="D172" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E172" s="2" t="inlineStr">
@@ -8849,7 +8849,7 @@
       <c r="K172" s="2" t="inlineStr"/>
       <c r="L172" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -8866,12 +8866,12 @@
       </c>
       <c r="C173" s="2" t="inlineStr">
         <is>
-          <t>5:-10-0</t>
+          <t>Ho:5:-10-0</t>
         </is>
       </c>
       <c r="D173" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E173" s="2" t="inlineStr">
@@ -8901,7 +8901,7 @@
       <c r="K173" s="2" t="inlineStr"/>
       <c r="L173" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -8918,12 +8918,12 @@
       </c>
       <c r="C174" s="2" t="inlineStr">
         <is>
-          <t>5:-20--10</t>
+          <t>Ho:5:-20--10</t>
         </is>
       </c>
       <c r="D174" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E174" s="2" t="inlineStr">
@@ -8953,7 +8953,7 @@
       <c r="K174" s="2" t="inlineStr"/>
       <c r="L174" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -8970,12 +8970,12 @@
       </c>
       <c r="C175" s="2" t="inlineStr">
         <is>
-          <t>5:-30--20</t>
+          <t>Ho:5:-30--20</t>
         </is>
       </c>
       <c r="D175" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E175" s="2" t="inlineStr">
@@ -9005,7 +9005,7 @@
       <c r="K175" s="2" t="inlineStr"/>
       <c r="L175" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -9022,12 +9022,12 @@
       </c>
       <c r="C176" s="2" t="inlineStr">
         <is>
-          <t>5:-40--30</t>
+          <t>Ho:5:-40--30</t>
         </is>
       </c>
       <c r="D176" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E176" s="2" t="inlineStr">
@@ -9057,7 +9057,7 @@
       <c r="K176" s="2" t="inlineStr"/>
       <c r="L176" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -9074,12 +9074,12 @@
       </c>
       <c r="C177" s="2" t="inlineStr">
         <is>
-          <t>5:-50--40</t>
+          <t>Ho:5:-50--40</t>
         </is>
       </c>
       <c r="D177" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E177" s="2" t="inlineStr">
@@ -9109,7 +9109,7 @@
       <c r="K177" s="2" t="inlineStr"/>
       <c r="L177" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -9126,12 +9126,12 @@
       </c>
       <c r="C178" s="2" t="inlineStr">
         <is>
-          <t>5:-60--50</t>
+          <t>Ho:5:-60--50</t>
         </is>
       </c>
       <c r="D178" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E178" s="2" t="inlineStr">
@@ -9161,7 +9161,7 @@
       <c r="K178" s="2" t="inlineStr"/>
       <c r="L178" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -9178,12 +9178,12 @@
       </c>
       <c r="C179" s="2" t="inlineStr">
         <is>
-          <t>5:-70--60</t>
+          <t>Ho:5:-70--60</t>
         </is>
       </c>
       <c r="D179" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E179" s="2" t="inlineStr">
@@ -9213,7 +9213,7 @@
       <c r="K179" s="2" t="inlineStr"/>
       <c r="L179" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -9230,12 +9230,12 @@
       </c>
       <c r="C180" s="2" t="inlineStr">
         <is>
-          <t>5:-80--70</t>
+          <t>Ho:5:-80--70</t>
         </is>
       </c>
       <c r="D180" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E180" s="2" t="inlineStr">
@@ -9265,7 +9265,7 @@
       <c r="K180" s="2" t="inlineStr"/>
       <c r="L180" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -9282,12 +9282,12 @@
       </c>
       <c r="C181" s="2" t="inlineStr">
         <is>
-          <t>5:-90--80</t>
+          <t>Ho:5:-90--80</t>
         </is>
       </c>
       <c r="D181" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E181" s="2" t="inlineStr">
@@ -9317,7 +9317,7 @@
       <c r="K181" s="2" t="inlineStr"/>
       <c r="L181" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -9334,12 +9334,12 @@
       </c>
       <c r="C182" s="2" t="inlineStr">
         <is>
-          <t>5:-100--90</t>
+          <t>Ho:5:-100--90</t>
         </is>
       </c>
       <c r="D182" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E182" s="2" t="inlineStr">
@@ -9369,7 +9369,7 @@
       <c r="K182" s="2" t="inlineStr"/>
       <c r="L182" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -9386,12 +9386,12 @@
       </c>
       <c r="C183" s="2" t="inlineStr">
         <is>
-          <t>5:-125--100</t>
+          <t>Ho:5:-125--100</t>
         </is>
       </c>
       <c r="D183" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E183" s="2" t="inlineStr">
@@ -9421,7 +9421,7 @@
       <c r="K183" s="2" t="inlineStr"/>
       <c r="L183" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -9438,12 +9438,12 @@
       </c>
       <c r="C184" s="2" t="inlineStr">
         <is>
-          <t>5:-150--125</t>
+          <t>Ho:5:-150--125</t>
         </is>
       </c>
       <c r="D184" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E184" s="2" t="inlineStr">
@@ -9473,7 +9473,7 @@
       <c r="K184" s="2" t="inlineStr"/>
       <c r="L184" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -9490,12 +9490,12 @@
       </c>
       <c r="C185" s="2" t="inlineStr">
         <is>
-          <t>5:-175--150</t>
+          <t>Ho:5:-175--150</t>
         </is>
       </c>
       <c r="D185" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E185" s="2" t="inlineStr">
@@ -9525,7 +9525,7 @@
       <c r="K185" s="2" t="inlineStr"/>
       <c r="L185" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -9542,12 +9542,12 @@
       </c>
       <c r="C186" s="2" t="inlineStr">
         <is>
-          <t>5:-200--175</t>
+          <t>Ho:5:-200--175</t>
         </is>
       </c>
       <c r="D186" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E186" s="2" t="inlineStr">
@@ -9577,7 +9577,7 @@
       <c r="K186" s="2" t="inlineStr"/>
       <c r="L186" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -9594,12 +9594,12 @@
       </c>
       <c r="C187" s="2" t="inlineStr">
         <is>
-          <t>5:-250--200</t>
+          <t>Ho:5:-250--200</t>
         </is>
       </c>
       <c r="D187" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E187" s="2" t="inlineStr">
@@ -9629,7 +9629,7 @@
       <c r="K187" s="2" t="inlineStr"/>
       <c r="L187" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -9646,12 +9646,12 @@
       </c>
       <c r="C188" s="2" t="inlineStr">
         <is>
-          <t>5:-300--250</t>
+          <t>Ho:5:-300--250</t>
         </is>
       </c>
       <c r="D188" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E188" s="2" t="inlineStr">
@@ -9681,7 +9681,7 @@
       <c r="K188" s="2" t="inlineStr"/>
       <c r="L188" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -9698,12 +9698,12 @@
       </c>
       <c r="C189" s="2" t="inlineStr">
         <is>
-          <t>6:20-30</t>
+          <t>Hu:6:20-30</t>
         </is>
       </c>
       <c r="D189" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E189" s="2" t="inlineStr">
@@ -9733,7 +9733,7 @@
       <c r="K189" s="2" t="inlineStr"/>
       <c r="L189" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -9750,12 +9750,12 @@
       </c>
       <c r="C190" s="2" t="inlineStr">
         <is>
-          <t>6:10-20</t>
+          <t>Hu:6:10-20</t>
         </is>
       </c>
       <c r="D190" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E190" s="2" t="inlineStr">
@@ -9785,7 +9785,7 @@
       <c r="K190" s="2" t="inlineStr"/>
       <c r="L190" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -9802,12 +9802,12 @@
       </c>
       <c r="C191" s="2" t="inlineStr">
         <is>
-          <t>6:0-10</t>
+          <t>Hu:6:0-10</t>
         </is>
       </c>
       <c r="D191" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E191" s="2" t="inlineStr">
@@ -9837,7 +9837,7 @@
       <c r="K191" s="2" t="inlineStr"/>
       <c r="L191" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -9854,12 +9854,12 @@
       </c>
       <c r="C192" s="2" t="inlineStr">
         <is>
-          <t>6:10-20</t>
+          <t>Hu:6:10-20</t>
         </is>
       </c>
       <c r="D192" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E192" s="2" t="inlineStr">
@@ -9889,7 +9889,7 @@
       <c r="K192" s="2" t="inlineStr"/>
       <c r="L192" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -9906,12 +9906,12 @@
       </c>
       <c r="C193" s="2" t="inlineStr">
         <is>
-          <t>6:0-10</t>
+          <t>Hu:6:0-10</t>
         </is>
       </c>
       <c r="D193" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E193" s="2" t="inlineStr">
@@ -9941,7 +9941,7 @@
       <c r="K193" s="2" t="inlineStr"/>
       <c r="L193" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -9958,12 +9958,12 @@
       </c>
       <c r="C194" s="2" t="inlineStr">
         <is>
-          <t>6:-10-0</t>
+          <t>Ho:6:-10-0</t>
         </is>
       </c>
       <c r="D194" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E194" s="2" t="inlineStr">
@@ -9993,7 +9993,7 @@
       <c r="K194" s="2" t="inlineStr"/>
       <c r="L194" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -10010,12 +10010,12 @@
       </c>
       <c r="C195" s="2" t="inlineStr">
         <is>
-          <t>6:-20--10</t>
+          <t>Ho:6:-20--10</t>
         </is>
       </c>
       <c r="D195" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E195" s="2" t="inlineStr">
@@ -10045,7 +10045,7 @@
       <c r="K195" s="2" t="inlineStr"/>
       <c r="L195" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -10062,12 +10062,12 @@
       </c>
       <c r="C196" s="2" t="inlineStr">
         <is>
-          <t>6:-30--20</t>
+          <t>Ho:6:-30--20</t>
         </is>
       </c>
       <c r="D196" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E196" s="2" t="inlineStr">
@@ -10097,7 +10097,7 @@
       <c r="K196" s="2" t="inlineStr"/>
       <c r="L196" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -10114,12 +10114,12 @@
       </c>
       <c r="C197" s="2" t="inlineStr">
         <is>
-          <t>6:-40--30</t>
+          <t>Ho:6:-40--30</t>
         </is>
       </c>
       <c r="D197" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E197" s="2" t="inlineStr">
@@ -10149,7 +10149,7 @@
       <c r="K197" s="2" t="inlineStr"/>
       <c r="L197" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -10166,12 +10166,12 @@
       </c>
       <c r="C198" s="2" t="inlineStr">
         <is>
-          <t>6:-50--40</t>
+          <t>Ho:6:-50--40</t>
         </is>
       </c>
       <c r="D198" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E198" s="2" t="inlineStr">
@@ -10201,7 +10201,7 @@
       <c r="K198" s="2" t="inlineStr"/>
       <c r="L198" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -10218,12 +10218,12 @@
       </c>
       <c r="C199" s="2" t="inlineStr">
         <is>
-          <t>6:-60--50</t>
+          <t>Ho:6:-60--50</t>
         </is>
       </c>
       <c r="D199" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E199" s="2" t="inlineStr">
@@ -10253,7 +10253,7 @@
       <c r="K199" s="2" t="inlineStr"/>
       <c r="L199" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -10270,12 +10270,12 @@
       </c>
       <c r="C200" s="2" t="inlineStr">
         <is>
-          <t>6:-70--60</t>
+          <t>Ho:6:-70--60</t>
         </is>
       </c>
       <c r="D200" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E200" s="2" t="inlineStr">
@@ -10305,7 +10305,7 @@
       <c r="K200" s="2" t="inlineStr"/>
       <c r="L200" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -10322,12 +10322,12 @@
       </c>
       <c r="C201" s="2" t="inlineStr">
         <is>
-          <t>6:-80--70</t>
+          <t>Ho:6:-80--70</t>
         </is>
       </c>
       <c r="D201" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E201" s="2" t="inlineStr">
@@ -10357,7 +10357,7 @@
       <c r="K201" s="2" t="inlineStr"/>
       <c r="L201" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -10374,12 +10374,12 @@
       </c>
       <c r="C202" s="2" t="inlineStr">
         <is>
-          <t>6:-90--80</t>
+          <t>Ho:6:-90--80</t>
         </is>
       </c>
       <c r="D202" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E202" s="2" t="inlineStr">
@@ -10409,7 +10409,7 @@
       <c r="K202" s="2" t="inlineStr"/>
       <c r="L202" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -10426,12 +10426,12 @@
       </c>
       <c r="C203" s="2" t="inlineStr">
         <is>
-          <t>6:-100--90</t>
+          <t>Ho:6:-100--90</t>
         </is>
       </c>
       <c r="D203" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E203" s="2" t="inlineStr">
@@ -10461,7 +10461,7 @@
       <c r="K203" s="2" t="inlineStr"/>
       <c r="L203" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -10478,12 +10478,12 @@
       </c>
       <c r="C204" s="2" t="inlineStr">
         <is>
-          <t>6:-125--100</t>
+          <t>Ho:6:-125--100</t>
         </is>
       </c>
       <c r="D204" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E204" s="2" t="inlineStr">
@@ -10513,7 +10513,7 @@
       <c r="K204" s="2" t="inlineStr"/>
       <c r="L204" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -10530,12 +10530,12 @@
       </c>
       <c r="C205" s="2" t="inlineStr">
         <is>
-          <t>6:-150--125</t>
+          <t>Ho:6:-150--125</t>
         </is>
       </c>
       <c r="D205" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E205" s="2" t="inlineStr">
@@ -10565,7 +10565,7 @@
       <c r="K205" s="2" t="inlineStr"/>
       <c r="L205" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -10582,12 +10582,12 @@
       </c>
       <c r="C206" s="2" t="inlineStr">
         <is>
-          <t>6:-175--150</t>
+          <t>Ho:6:-175--150</t>
         </is>
       </c>
       <c r="D206" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E206" s="2" t="inlineStr">
@@ -10617,7 +10617,7 @@
       <c r="K206" s="2" t="inlineStr"/>
       <c r="L206" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -10634,12 +10634,12 @@
       </c>
       <c r="C207" s="2" t="inlineStr">
         <is>
-          <t>6:-200--175</t>
+          <t>Ho:6:-200--175</t>
         </is>
       </c>
       <c r="D207" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E207" s="2" t="inlineStr">
@@ -10669,7 +10669,7 @@
       <c r="K207" s="2" t="inlineStr"/>
       <c r="L207" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -10686,12 +10686,12 @@
       </c>
       <c r="C208" s="2" t="inlineStr">
         <is>
-          <t>6:-250--200</t>
+          <t>Ho:6:-250--200</t>
         </is>
       </c>
       <c r="D208" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E208" s="2" t="inlineStr">
@@ -10721,7 +10721,7 @@
       <c r="K208" s="2" t="inlineStr"/>
       <c r="L208" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -10738,12 +10738,12 @@
       </c>
       <c r="C209" s="2" t="inlineStr">
         <is>
-          <t>7:0-10</t>
+          <t>Hu:7:0-10</t>
         </is>
       </c>
       <c r="D209" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E209" s="2" t="inlineStr">
@@ -10773,7 +10773,7 @@
       <c r="K209" s="2" t="inlineStr"/>
       <c r="L209" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -10790,12 +10790,12 @@
       </c>
       <c r="C210" s="2" t="inlineStr">
         <is>
-          <t>7:20-22</t>
+          <t>Hu:7:20-22</t>
         </is>
       </c>
       <c r="D210" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E210" s="2" t="inlineStr">
@@ -10825,7 +10825,7 @@
       <c r="K210" s="2" t="inlineStr"/>
       <c r="L210" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -10842,12 +10842,12 @@
       </c>
       <c r="C211" s="2" t="inlineStr">
         <is>
-          <t>7:10-20</t>
+          <t>Hu:7:10-20</t>
         </is>
       </c>
       <c r="D211" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E211" s="2" t="inlineStr">
@@ -10877,7 +10877,7 @@
       <c r="K211" s="2" t="inlineStr"/>
       <c r="L211" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -10894,12 +10894,12 @@
       </c>
       <c r="C212" s="2" t="inlineStr">
         <is>
-          <t>7:0-10</t>
+          <t>Hu:7:0-10</t>
         </is>
       </c>
       <c r="D212" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E212" s="2" t="inlineStr">
@@ -10929,7 +10929,7 @@
       <c r="K212" s="2" t="inlineStr"/>
       <c r="L212" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -10946,12 +10946,12 @@
       </c>
       <c r="C213" s="2" t="inlineStr">
         <is>
-          <t>7:-10-0</t>
+          <t>Ho:7:-10-0</t>
         </is>
       </c>
       <c r="D213" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E213" s="2" t="inlineStr">
@@ -10981,7 +10981,7 @@
       <c r="K213" s="2" t="inlineStr"/>
       <c r="L213" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -10998,12 +10998,12 @@
       </c>
       <c r="C214" s="2" t="inlineStr">
         <is>
-          <t>7:-20--10</t>
+          <t>Ho:7:-20--10</t>
         </is>
       </c>
       <c r="D214" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E214" s="2" t="inlineStr">
@@ -11033,7 +11033,7 @@
       <c r="K214" s="2" t="inlineStr"/>
       <c r="L214" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -11050,12 +11050,12 @@
       </c>
       <c r="C215" s="2" t="inlineStr">
         <is>
-          <t>7:-30--20</t>
+          <t>Ho:7:-30--20</t>
         </is>
       </c>
       <c r="D215" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E215" s="2" t="inlineStr">
@@ -11085,7 +11085,7 @@
       <c r="K215" s="2" t="inlineStr"/>
       <c r="L215" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -11102,12 +11102,12 @@
       </c>
       <c r="C216" s="2" t="inlineStr">
         <is>
-          <t>7:-40--30</t>
+          <t>Ho:7:-40--30</t>
         </is>
       </c>
       <c r="D216" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E216" s="2" t="inlineStr">
@@ -11137,7 +11137,7 @@
       <c r="K216" s="2" t="inlineStr"/>
       <c r="L216" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -11154,12 +11154,12 @@
       </c>
       <c r="C217" s="2" t="inlineStr">
         <is>
-          <t>7:-50--40</t>
+          <t>Ho:7:-50--40</t>
         </is>
       </c>
       <c r="D217" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E217" s="2" t="inlineStr">
@@ -11189,7 +11189,7 @@
       <c r="K217" s="2" t="inlineStr"/>
       <c r="L217" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -11206,12 +11206,12 @@
       </c>
       <c r="C218" s="2" t="inlineStr">
         <is>
-          <t>7:-60--50</t>
+          <t>Ho:7:-60--50</t>
         </is>
       </c>
       <c r="D218" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E218" s="2" t="inlineStr">
@@ -11241,7 +11241,7 @@
       <c r="K218" s="2" t="inlineStr"/>
       <c r="L218" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -11258,12 +11258,12 @@
       </c>
       <c r="C219" s="2" t="inlineStr">
         <is>
-          <t>7:-70--60</t>
+          <t>Ho:7:-70--60</t>
         </is>
       </c>
       <c r="D219" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E219" s="2" t="inlineStr">
@@ -11293,7 +11293,7 @@
       <c r="K219" s="2" t="inlineStr"/>
       <c r="L219" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -11310,12 +11310,12 @@
       </c>
       <c r="C220" s="2" t="inlineStr">
         <is>
-          <t>7:-80--70</t>
+          <t>Ho:7:-80--70</t>
         </is>
       </c>
       <c r="D220" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E220" s="2" t="inlineStr">
@@ -11345,7 +11345,7 @@
       <c r="K220" s="2" t="inlineStr"/>
       <c r="L220" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -11362,12 +11362,12 @@
       </c>
       <c r="C221" s="2" t="inlineStr">
         <is>
-          <t>7:-90--80</t>
+          <t>Ho:7:-90--80</t>
         </is>
       </c>
       <c r="D221" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E221" s="2" t="inlineStr">
@@ -11397,7 +11397,7 @@
       <c r="K221" s="2" t="inlineStr"/>
       <c r="L221" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -11414,12 +11414,12 @@
       </c>
       <c r="C222" s="2" t="inlineStr">
         <is>
-          <t>7:-100--90</t>
+          <t>Ho:7:-100--90</t>
         </is>
       </c>
       <c r="D222" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E222" s="2" t="inlineStr">
@@ -11449,7 +11449,7 @@
       <c r="K222" s="2" t="inlineStr"/>
       <c r="L222" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -11466,12 +11466,12 @@
       </c>
       <c r="C223" s="2" t="inlineStr">
         <is>
-          <t>7:-125--100</t>
+          <t>Ho:7:-125--100</t>
         </is>
       </c>
       <c r="D223" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E223" s="2" t="inlineStr">
@@ -11501,7 +11501,7 @@
       <c r="K223" s="2" t="inlineStr"/>
       <c r="L223" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -11518,12 +11518,12 @@
       </c>
       <c r="C224" s="2" t="inlineStr">
         <is>
-          <t>7:-150--125</t>
+          <t>Ho:7:-150--125</t>
         </is>
       </c>
       <c r="D224" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E224" s="2" t="inlineStr">
@@ -11553,7 +11553,7 @@
       <c r="K224" s="2" t="inlineStr"/>
       <c r="L224" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -11570,12 +11570,12 @@
       </c>
       <c r="C225" s="2" t="inlineStr">
         <is>
-          <t>7:-175--150</t>
+          <t>Ho:7:-175--150</t>
         </is>
       </c>
       <c r="D225" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E225" s="2" t="inlineStr">
@@ -11605,7 +11605,7 @@
       <c r="K225" s="2" t="inlineStr"/>
       <c r="L225" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -11622,12 +11622,12 @@
       </c>
       <c r="C226" s="2" t="inlineStr">
         <is>
-          <t>7:-200--175</t>
+          <t>Ho:7:-200--175</t>
         </is>
       </c>
       <c r="D226" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E226" s="2" t="inlineStr">
@@ -11657,7 +11657,7 @@
       <c r="K226" s="2" t="inlineStr"/>
       <c r="L226" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -11674,12 +11674,12 @@
       </c>
       <c r="C227" s="2" t="inlineStr">
         <is>
-          <t>7:-250--200</t>
+          <t>Ho:7:-250--200</t>
         </is>
       </c>
       <c r="D227" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E227" s="2" t="inlineStr">
@@ -11709,7 +11709,7 @@
       <c r="K227" s="2" t="inlineStr"/>
       <c r="L227" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -11726,12 +11726,12 @@
       </c>
       <c r="C228" s="2" t="inlineStr">
         <is>
-          <t>7:-300--250</t>
+          <t>Ho:7:-300--250</t>
         </is>
       </c>
       <c r="D228" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E228" s="2" t="inlineStr">
@@ -11761,7 +11761,7 @@
       <c r="K228" s="2" t="inlineStr"/>
       <c r="L228" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -11778,12 +11778,12 @@
       </c>
       <c r="C229" s="2" t="inlineStr">
         <is>
-          <t>8:10-20</t>
+          <t>Hu:8:10-20</t>
         </is>
       </c>
       <c r="D229" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E229" s="2" t="inlineStr">
@@ -11813,7 +11813,7 @@
       <c r="K229" s="2" t="inlineStr"/>
       <c r="L229" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -11830,12 +11830,12 @@
       </c>
       <c r="C230" s="2" t="inlineStr">
         <is>
-          <t>8:0-10</t>
+          <t>Hu:8:0-10</t>
         </is>
       </c>
       <c r="D230" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E230" s="2" t="inlineStr">
@@ -11865,7 +11865,7 @@
       <c r="K230" s="2" t="inlineStr"/>
       <c r="L230" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -11882,12 +11882,12 @@
       </c>
       <c r="C231" s="2" t="inlineStr">
         <is>
-          <t>8:-10-0</t>
+          <t>Hu:8:-10-0</t>
         </is>
       </c>
       <c r="D231" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E231" s="2" t="inlineStr">
@@ -11917,7 +11917,7 @@
       <c r="K231" s="2" t="inlineStr"/>
       <c r="L231" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -11934,12 +11934,12 @@
       </c>
       <c r="C232" s="2" t="inlineStr">
         <is>
-          <t>8:-10-0</t>
+          <t>Ho:8:-10-0</t>
         </is>
       </c>
       <c r="D232" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E232" s="2" t="inlineStr">
@@ -11969,7 +11969,7 @@
       <c r="K232" s="2" t="inlineStr"/>
       <c r="L232" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -11986,12 +11986,12 @@
       </c>
       <c r="C233" s="2" t="inlineStr">
         <is>
-          <t>8:-20--10</t>
+          <t>Ho:8:-20--10</t>
         </is>
       </c>
       <c r="D233" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E233" s="2" t="inlineStr">
@@ -12021,7 +12021,7 @@
       <c r="K233" s="2" t="inlineStr"/>
       <c r="L233" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -12038,12 +12038,12 @@
       </c>
       <c r="C234" s="2" t="inlineStr">
         <is>
-          <t>8:-30--20</t>
+          <t>Ho:8:-30--20</t>
         </is>
       </c>
       <c r="D234" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E234" s="2" t="inlineStr">
@@ -12073,7 +12073,7 @@
       <c r="K234" s="2" t="inlineStr"/>
       <c r="L234" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -12090,12 +12090,12 @@
       </c>
       <c r="C235" s="2" t="inlineStr">
         <is>
-          <t>8:-40--30</t>
+          <t>Ho:8:-40--30</t>
         </is>
       </c>
       <c r="D235" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E235" s="2" t="inlineStr">
@@ -12125,7 +12125,7 @@
       <c r="K235" s="2" t="inlineStr"/>
       <c r="L235" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -12142,12 +12142,12 @@
       </c>
       <c r="C236" s="2" t="inlineStr">
         <is>
-          <t>8:-50--40</t>
+          <t>Ho:8:-50--40</t>
         </is>
       </c>
       <c r="D236" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E236" s="2" t="inlineStr">
@@ -12177,7 +12177,7 @@
       <c r="K236" s="2" t="inlineStr"/>
       <c r="L236" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -12194,12 +12194,12 @@
       </c>
       <c r="C237" s="2" t="inlineStr">
         <is>
-          <t>8:-60--50</t>
+          <t>Ho:8:-60--50</t>
         </is>
       </c>
       <c r="D237" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E237" s="2" t="inlineStr">
@@ -12229,7 +12229,7 @@
       <c r="K237" s="2" t="inlineStr"/>
       <c r="L237" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -12246,12 +12246,12 @@
       </c>
       <c r="C238" s="2" t="inlineStr">
         <is>
-          <t>8:-70--60</t>
+          <t>Ho:8:-70--60</t>
         </is>
       </c>
       <c r="D238" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E238" s="2" t="inlineStr">
@@ -12281,7 +12281,7 @@
       <c r="K238" s="2" t="inlineStr"/>
       <c r="L238" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -12298,12 +12298,12 @@
       </c>
       <c r="C239" s="2" t="inlineStr">
         <is>
-          <t>8:-80--70</t>
+          <t>Ho:8:-80--70</t>
         </is>
       </c>
       <c r="D239" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E239" s="2" t="inlineStr">
@@ -12333,7 +12333,7 @@
       <c r="K239" s="2" t="inlineStr"/>
       <c r="L239" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -12350,12 +12350,12 @@
       </c>
       <c r="C240" s="2" t="inlineStr">
         <is>
-          <t>8:-90--80</t>
+          <t>Ho:8:-90--80</t>
         </is>
       </c>
       <c r="D240" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E240" s="2" t="inlineStr">
@@ -12385,7 +12385,7 @@
       <c r="K240" s="2" t="inlineStr"/>
       <c r="L240" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -12402,12 +12402,12 @@
       </c>
       <c r="C241" s="2" t="inlineStr">
         <is>
-          <t>8:-100--90</t>
+          <t>Ho:8:-100--90</t>
         </is>
       </c>
       <c r="D241" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E241" s="2" t="inlineStr">
@@ -12437,7 +12437,7 @@
       <c r="K241" s="2" t="inlineStr"/>
       <c r="L241" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -12454,12 +12454,12 @@
       </c>
       <c r="C242" s="2" t="inlineStr">
         <is>
-          <t>8:-125--100</t>
+          <t>Ho:8:-125--100</t>
         </is>
       </c>
       <c r="D242" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E242" s="2" t="inlineStr">
@@ -12489,7 +12489,7 @@
       <c r="K242" s="2" t="inlineStr"/>
       <c r="L242" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -12506,12 +12506,12 @@
       </c>
       <c r="C243" s="2" t="inlineStr">
         <is>
-          <t>8:-150--125</t>
+          <t>Ho:8:-150--125</t>
         </is>
       </c>
       <c r="D243" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E243" s="2" t="inlineStr">
@@ -12541,7 +12541,7 @@
       <c r="K243" s="2" t="inlineStr"/>
       <c r="L243" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -12558,12 +12558,12 @@
       </c>
       <c r="C244" s="2" t="inlineStr">
         <is>
-          <t>8:-175--150</t>
+          <t>Ho:8:-175--150</t>
         </is>
       </c>
       <c r="D244" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E244" s="2" t="inlineStr">
@@ -12593,7 +12593,7 @@
       <c r="K244" s="2" t="inlineStr"/>
       <c r="L244" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -12610,12 +12610,12 @@
       </c>
       <c r="C245" s="2" t="inlineStr">
         <is>
-          <t>8:-200--175</t>
+          <t>Ho:8:-200--175</t>
         </is>
       </c>
       <c r="D245" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E245" s="2" t="inlineStr">
@@ -12645,7 +12645,7 @@
       <c r="K245" s="2" t="inlineStr"/>
       <c r="L245" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -12662,12 +12662,12 @@
       </c>
       <c r="C246" s="2" t="inlineStr">
         <is>
-          <t>9:10-18</t>
+          <t>Hu:9:10-18</t>
         </is>
       </c>
       <c r="D246" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E246" s="2" t="inlineStr">
@@ -12697,7 +12697,7 @@
       <c r="K246" s="2" t="inlineStr"/>
       <c r="L246" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -12714,12 +12714,12 @@
       </c>
       <c r="C247" s="2" t="inlineStr">
         <is>
-          <t>9:0-10</t>
+          <t>Hu:9:0-10</t>
         </is>
       </c>
       <c r="D247" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E247" s="2" t="inlineStr">
@@ -12749,7 +12749,7 @@
       <c r="K247" s="2" t="inlineStr"/>
       <c r="L247" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -12766,12 +12766,12 @@
       </c>
       <c r="C248" s="2" t="inlineStr">
         <is>
-          <t>9:-10-0</t>
+          <t>Ho:9:-10-0</t>
         </is>
       </c>
       <c r="D248" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E248" s="2" t="inlineStr">
@@ -12801,7 +12801,7 @@
       <c r="K248" s="2" t="inlineStr"/>
       <c r="L248" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -12818,12 +12818,12 @@
       </c>
       <c r="C249" s="2" t="inlineStr">
         <is>
-          <t>9:-20--10</t>
+          <t>Ho:9:-20--10</t>
         </is>
       </c>
       <c r="D249" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E249" s="2" t="inlineStr">
@@ -12853,7 +12853,7 @@
       <c r="K249" s="2" t="inlineStr"/>
       <c r="L249" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -12870,12 +12870,12 @@
       </c>
       <c r="C250" s="2" t="inlineStr">
         <is>
-          <t>9:-30--20</t>
+          <t>Ho:9:-30--20</t>
         </is>
       </c>
       <c r="D250" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E250" s="2" t="inlineStr">
@@ -12905,7 +12905,7 @@
       <c r="K250" s="2" t="inlineStr"/>
       <c r="L250" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -12922,12 +12922,12 @@
       </c>
       <c r="C251" s="2" t="inlineStr">
         <is>
-          <t>9:-40--30</t>
+          <t>Ho:9:-40--30</t>
         </is>
       </c>
       <c r="D251" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E251" s="2" t="inlineStr">
@@ -12957,7 +12957,7 @@
       <c r="K251" s="2" t="inlineStr"/>
       <c r="L251" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -12974,12 +12974,12 @@
       </c>
       <c r="C252" s="2" t="inlineStr">
         <is>
-          <t>9:-50--40</t>
+          <t>Ho:9:-50--40</t>
         </is>
       </c>
       <c r="D252" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E252" s="2" t="inlineStr">
@@ -13009,7 +13009,7 @@
       <c r="K252" s="2" t="inlineStr"/>
       <c r="L252" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -13026,12 +13026,12 @@
       </c>
       <c r="C253" s="2" t="inlineStr">
         <is>
-          <t>9:-60--50</t>
+          <t>Ho:9:-60--50</t>
         </is>
       </c>
       <c r="D253" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E253" s="2" t="inlineStr">
@@ -13061,7 +13061,7 @@
       <c r="K253" s="2" t="inlineStr"/>
       <c r="L253" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -13078,12 +13078,12 @@
       </c>
       <c r="C254" s="2" t="inlineStr">
         <is>
-          <t>9:-70--60</t>
+          <t>Ho:9:-70--60</t>
         </is>
       </c>
       <c r="D254" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E254" s="2" t="inlineStr">
@@ -13113,7 +13113,7 @@
       <c r="K254" s="2" t="inlineStr"/>
       <c r="L254" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -13130,12 +13130,12 @@
       </c>
       <c r="C255" s="2" t="inlineStr">
         <is>
-          <t>9:-80--70</t>
+          <t>Ho:9:-80--70</t>
         </is>
       </c>
       <c r="D255" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E255" s="2" t="inlineStr">
@@ -13165,7 +13165,7 @@
       <c r="K255" s="2" t="inlineStr"/>
       <c r="L255" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -13182,12 +13182,12 @@
       </c>
       <c r="C256" s="2" t="inlineStr">
         <is>
-          <t>9:-90--80</t>
+          <t>Ho:9:-90--80</t>
         </is>
       </c>
       <c r="D256" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E256" s="2" t="inlineStr">
@@ -13217,7 +13217,7 @@
       <c r="K256" s="2" t="inlineStr"/>
       <c r="L256" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -13234,12 +13234,12 @@
       </c>
       <c r="C257" s="2" t="inlineStr">
         <is>
-          <t>9:-100--90</t>
+          <t>Ho:9:-100--90</t>
         </is>
       </c>
       <c r="D257" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E257" s="2" t="inlineStr">
@@ -13269,7 +13269,7 @@
       <c r="K257" s="2" t="inlineStr"/>
       <c r="L257" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -13286,12 +13286,12 @@
       </c>
       <c r="C258" s="2" t="inlineStr">
         <is>
-          <t>9:-125--100</t>
+          <t>Ho:9:-125--100</t>
         </is>
       </c>
       <c r="D258" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E258" s="2" t="inlineStr">
@@ -13321,7 +13321,7 @@
       <c r="K258" s="2" t="inlineStr"/>
       <c r="L258" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -13338,12 +13338,12 @@
       </c>
       <c r="C259" s="2" t="inlineStr">
         <is>
-          <t>9:-150--125</t>
+          <t>Ho:9:-150--125</t>
         </is>
       </c>
       <c r="D259" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E259" s="2" t="inlineStr">
@@ -13373,7 +13373,7 @@
       <c r="K259" s="2" t="inlineStr"/>
       <c r="L259" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -13390,12 +13390,12 @@
       </c>
       <c r="C260" s="2" t="inlineStr">
         <is>
-          <t>9:-175--150</t>
+          <t>Ho:9:-175--150</t>
         </is>
       </c>
       <c r="D260" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E260" s="2" t="inlineStr">
@@ -13425,7 +13425,7 @@
       <c r="K260" s="2" t="inlineStr"/>
       <c r="L260" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -13442,12 +13442,12 @@
       </c>
       <c r="C261" s="2" t="inlineStr">
         <is>
-          <t>9:-200--175</t>
+          <t>Ho:9:-200--175</t>
         </is>
       </c>
       <c r="D261" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E261" s="2" t="inlineStr">
@@ -13477,7 +13477,7 @@
       <c r="K261" s="2" t="inlineStr"/>
       <c r="L261" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -13494,12 +13494,12 @@
       </c>
       <c r="C262" s="2" t="inlineStr">
         <is>
-          <t>9:-250--200</t>
+          <t>Ho:9:-250--200</t>
         </is>
       </c>
       <c r="D262" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E262" s="2" t="inlineStr">
@@ -13529,7 +13529,7 @@
       <c r="K262" s="2" t="inlineStr"/>
       <c r="L262" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -13546,12 +13546,12 @@
       </c>
       <c r="C263" s="2" t="inlineStr">
         <is>
-          <t>9:-300--250</t>
+          <t>Ho:9:-300--250</t>
         </is>
       </c>
       <c r="D263" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E263" s="2" t="inlineStr">
@@ -13581,7 +13581,7 @@
       <c r="K263" s="2" t="inlineStr"/>
       <c r="L263" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -13598,12 +13598,12 @@
       </c>
       <c r="C264" s="2" t="inlineStr">
         <is>
-          <t>10:20-29</t>
+          <t>Hu:10:20-29</t>
         </is>
       </c>
       <c r="D264" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E264" s="2" t="inlineStr">
@@ -13633,7 +13633,7 @@
       <c r="K264" s="2" t="inlineStr"/>
       <c r="L264" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -13650,12 +13650,12 @@
       </c>
       <c r="C265" s="2" t="inlineStr">
         <is>
-          <t>10:10-20</t>
+          <t>Hu:10:10-20</t>
         </is>
       </c>
       <c r="D265" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E265" s="2" t="inlineStr">
@@ -13685,7 +13685,7 @@
       <c r="K265" s="2" t="inlineStr"/>
       <c r="L265" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -13702,12 +13702,12 @@
       </c>
       <c r="C266" s="2" t="inlineStr">
         <is>
-          <t>10:0-10</t>
+          <t>Hu:10:0-10</t>
         </is>
       </c>
       <c r="D266" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E266" s="2" t="inlineStr">
@@ -13737,7 +13737,7 @@
       <c r="K266" s="2" t="inlineStr"/>
       <c r="L266" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -13754,12 +13754,12 @@
       </c>
       <c r="C267" s="2" t="inlineStr">
         <is>
-          <t>10:-10-0</t>
+          <t>Ho:10:-10-0</t>
         </is>
       </c>
       <c r="D267" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E267" s="2" t="inlineStr">
@@ -13789,7 +13789,7 @@
       <c r="K267" s="2" t="inlineStr"/>
       <c r="L267" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -13806,12 +13806,12 @@
       </c>
       <c r="C268" s="2" t="inlineStr">
         <is>
-          <t>10:-20--10</t>
+          <t>Ho:10:-20--10</t>
         </is>
       </c>
       <c r="D268" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E268" s="2" t="inlineStr">
@@ -13841,7 +13841,7 @@
       <c r="K268" s="2" t="inlineStr"/>
       <c r="L268" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -13858,12 +13858,12 @@
       </c>
       <c r="C269" s="2" t="inlineStr">
         <is>
-          <t>10:-30--20</t>
+          <t>Ho:10:-30--20</t>
         </is>
       </c>
       <c r="D269" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E269" s="2" t="inlineStr">
@@ -13893,7 +13893,7 @@
       <c r="K269" s="2" t="inlineStr"/>
       <c r="L269" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -13910,12 +13910,12 @@
       </c>
       <c r="C270" s="2" t="inlineStr">
         <is>
-          <t>10:-40--30</t>
+          <t>Ho:10:-40--30</t>
         </is>
       </c>
       <c r="D270" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E270" s="2" t="inlineStr">
@@ -13945,7 +13945,7 @@
       <c r="K270" s="2" t="inlineStr"/>
       <c r="L270" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -13962,12 +13962,12 @@
       </c>
       <c r="C271" s="2" t="inlineStr">
         <is>
-          <t>10:-50--40</t>
+          <t>Ho:10:-50--40</t>
         </is>
       </c>
       <c r="D271" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E271" s="2" t="inlineStr">
@@ -13997,7 +13997,7 @@
       <c r="K271" s="2" t="inlineStr"/>
       <c r="L271" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -14014,12 +14014,12 @@
       </c>
       <c r="C272" s="2" t="inlineStr">
         <is>
-          <t>10:-60--50</t>
+          <t>Ho:10:-60--50</t>
         </is>
       </c>
       <c r="D272" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E272" s="2" t="inlineStr">
@@ -14049,7 +14049,7 @@
       <c r="K272" s="2" t="inlineStr"/>
       <c r="L272" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -14066,12 +14066,12 @@
       </c>
       <c r="C273" s="2" t="inlineStr">
         <is>
-          <t>10:-70--60</t>
+          <t>Ho:10:-70--60</t>
         </is>
       </c>
       <c r="D273" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E273" s="2" t="inlineStr">
@@ -14101,7 +14101,7 @@
       <c r="K273" s="2" t="inlineStr"/>
       <c r="L273" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -14118,12 +14118,12 @@
       </c>
       <c r="C274" s="2" t="inlineStr">
         <is>
-          <t>10:-80--70</t>
+          <t>Ho:10:-80--70</t>
         </is>
       </c>
       <c r="D274" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E274" s="2" t="inlineStr">
@@ -14153,7 +14153,7 @@
       <c r="K274" s="2" t="inlineStr"/>
       <c r="L274" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -14170,12 +14170,12 @@
       </c>
       <c r="C275" s="2" t="inlineStr">
         <is>
-          <t>10:-90--80</t>
+          <t>Ho:10:-90--80</t>
         </is>
       </c>
       <c r="D275" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E275" s="2" t="inlineStr">
@@ -14205,7 +14205,7 @@
       <c r="K275" s="2" t="inlineStr"/>
       <c r="L275" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -14222,12 +14222,12 @@
       </c>
       <c r="C276" s="2" t="inlineStr">
         <is>
-          <t>10:-100--90</t>
+          <t>Ho:10:-100--90</t>
         </is>
       </c>
       <c r="D276" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E276" s="2" t="inlineStr">
@@ -14257,7 +14257,7 @@
       <c r="K276" s="2" t="inlineStr"/>
       <c r="L276" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -14274,12 +14274,12 @@
       </c>
       <c r="C277" s="2" t="inlineStr">
         <is>
-          <t>10:-125--100</t>
+          <t>Ho:10:-125--100</t>
         </is>
       </c>
       <c r="D277" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E277" s="2" t="inlineStr">
@@ -14309,7 +14309,7 @@
       <c r="K277" s="2" t="inlineStr"/>
       <c r="L277" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -14326,12 +14326,12 @@
       </c>
       <c r="C278" s="2" t="inlineStr">
         <is>
-          <t>10:-150--125</t>
+          <t>Ho:10:-150--125</t>
         </is>
       </c>
       <c r="D278" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E278" s="2" t="inlineStr">
@@ -14361,7 +14361,7 @@
       <c r="K278" s="2" t="inlineStr"/>
       <c r="L278" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -14378,12 +14378,12 @@
       </c>
       <c r="C279" s="2" t="inlineStr">
         <is>
-          <t>10:-175--150</t>
+          <t>Ho:10:-175--150</t>
         </is>
       </c>
       <c r="D279" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E279" s="2" t="inlineStr">
@@ -14413,7 +14413,7 @@
       <c r="K279" s="2" t="inlineStr"/>
       <c r="L279" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -14430,12 +14430,12 @@
       </c>
       <c r="C280" s="2" t="inlineStr">
         <is>
-          <t>10:-200--175</t>
+          <t>Ho:10:-200--175</t>
         </is>
       </c>
       <c r="D280" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E280" s="2" t="inlineStr">
@@ -14465,7 +14465,7 @@
       <c r="K280" s="2" t="inlineStr"/>
       <c r="L280" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -14482,12 +14482,12 @@
       </c>
       <c r="C281" s="2" t="inlineStr">
         <is>
-          <t>10:-225--200</t>
+          <t>Ho:10:-225--200</t>
         </is>
       </c>
       <c r="D281" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E281" s="2" t="inlineStr">
@@ -14517,7 +14517,7 @@
       <c r="K281" s="2" t="inlineStr"/>
       <c r="L281" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -14534,12 +14534,12 @@
       </c>
       <c r="C282" s="2" t="inlineStr">
         <is>
-          <t>10:-255--225</t>
+          <t>Ho:10:-255--225</t>
         </is>
       </c>
       <c r="D282" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E282" s="2" t="inlineStr">
@@ -14569,7 +14569,7 @@
       <c r="K282" s="2" t="inlineStr"/>
       <c r="L282" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -14586,12 +14586,12 @@
       </c>
       <c r="C283" s="2" t="inlineStr">
         <is>
-          <t>10:-275--255</t>
+          <t>Ho:10:-275--255</t>
         </is>
       </c>
       <c r="D283" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E283" s="2" t="inlineStr">
@@ -14621,7 +14621,7 @@
       <c r="K283" s="2" t="inlineStr"/>
       <c r="L283" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -14638,12 +14638,12 @@
       </c>
       <c r="C284" s="2" t="inlineStr">
         <is>
-          <t>11:10-18</t>
+          <t>Hu:11:10-18</t>
         </is>
       </c>
       <c r="D284" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E284" s="2" t="inlineStr">
@@ -14673,7 +14673,7 @@
       <c r="K284" s="2" t="inlineStr"/>
       <c r="L284" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -14690,12 +14690,12 @@
       </c>
       <c r="C285" s="2" t="inlineStr">
         <is>
-          <t>11:0-10</t>
+          <t>Hu:11:0-10</t>
         </is>
       </c>
       <c r="D285" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E285" s="2" t="inlineStr">
@@ -14725,7 +14725,7 @@
       <c r="K285" s="2" t="inlineStr"/>
       <c r="L285" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -14742,12 +14742,12 @@
       </c>
       <c r="C286" s="2" t="inlineStr">
         <is>
-          <t>11:-10-0</t>
+          <t>Ho:11:-10-0</t>
         </is>
       </c>
       <c r="D286" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E286" s="2" t="inlineStr">
@@ -14777,7 +14777,7 @@
       <c r="K286" s="2" t="inlineStr"/>
       <c r="L286" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -14794,12 +14794,12 @@
       </c>
       <c r="C287" s="2" t="inlineStr">
         <is>
-          <t>11:-20--10</t>
+          <t>Ho:11:-20--10</t>
         </is>
       </c>
       <c r="D287" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E287" s="2" t="inlineStr">
@@ -14829,7 +14829,7 @@
       <c r="K287" s="2" t="inlineStr"/>
       <c r="L287" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -14846,12 +14846,12 @@
       </c>
       <c r="C288" s="2" t="inlineStr">
         <is>
-          <t>11:-30--20</t>
+          <t>Ho:11:-30--20</t>
         </is>
       </c>
       <c r="D288" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E288" s="2" t="inlineStr">
@@ -14881,7 +14881,7 @@
       <c r="K288" s="2" t="inlineStr"/>
       <c r="L288" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -14898,12 +14898,12 @@
       </c>
       <c r="C289" s="2" t="inlineStr">
         <is>
-          <t>11:-40--30</t>
+          <t>Ho:11:-40--30</t>
         </is>
       </c>
       <c r="D289" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E289" s="2" t="inlineStr">
@@ -14933,7 +14933,7 @@
       <c r="K289" s="2" t="inlineStr"/>
       <c r="L289" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -14950,12 +14950,12 @@
       </c>
       <c r="C290" s="2" t="inlineStr">
         <is>
-          <t>11:-50--40</t>
+          <t>Ho:11:-50--40</t>
         </is>
       </c>
       <c r="D290" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E290" s="2" t="inlineStr">
@@ -14985,7 +14985,7 @@
       <c r="K290" s="2" t="inlineStr"/>
       <c r="L290" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -15002,12 +15002,12 @@
       </c>
       <c r="C291" s="2" t="inlineStr">
         <is>
-          <t>11:-60--50</t>
+          <t>Ho:11:-60--50</t>
         </is>
       </c>
       <c r="D291" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E291" s="2" t="inlineStr">
@@ -15037,7 +15037,7 @@
       <c r="K291" s="2" t="inlineStr"/>
       <c r="L291" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -15054,12 +15054,12 @@
       </c>
       <c r="C292" s="2" t="inlineStr">
         <is>
-          <t>11:-70--60</t>
+          <t>Ho:11:-70--60</t>
         </is>
       </c>
       <c r="D292" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E292" s="2" t="inlineStr">
@@ -15089,7 +15089,7 @@
       <c r="K292" s="2" t="inlineStr"/>
       <c r="L292" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -15106,12 +15106,12 @@
       </c>
       <c r="C293" s="2" t="inlineStr">
         <is>
-          <t>11:-80--70</t>
+          <t>Ho:11:-80--70</t>
         </is>
       </c>
       <c r="D293" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E293" s="2" t="inlineStr">
@@ -15141,7 +15141,7 @@
       <c r="K293" s="2" t="inlineStr"/>
       <c r="L293" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -15158,12 +15158,12 @@
       </c>
       <c r="C294" s="2" t="inlineStr">
         <is>
-          <t>11:-90--80</t>
+          <t>Ho:11:-90--80</t>
         </is>
       </c>
       <c r="D294" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E294" s="2" t="inlineStr">
@@ -15193,7 +15193,7 @@
       <c r="K294" s="2" t="inlineStr"/>
       <c r="L294" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -15210,12 +15210,12 @@
       </c>
       <c r="C295" s="2" t="inlineStr">
         <is>
-          <t>11:-100--90</t>
+          <t>Ho:11:-100--90</t>
         </is>
       </c>
       <c r="D295" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E295" s="2" t="inlineStr">
@@ -15245,7 +15245,7 @@
       <c r="K295" s="2" t="inlineStr"/>
       <c r="L295" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -15262,12 +15262,12 @@
       </c>
       <c r="C296" s="2" t="inlineStr">
         <is>
-          <t>11:-125--100</t>
+          <t>Ho:11:-125--100</t>
         </is>
       </c>
       <c r="D296" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E296" s="2" t="inlineStr">
@@ -15297,7 +15297,7 @@
       <c r="K296" s="2" t="inlineStr"/>
       <c r="L296" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -15314,12 +15314,12 @@
       </c>
       <c r="C297" s="2" t="inlineStr">
         <is>
-          <t>11:-150--125</t>
+          <t>Ho:11:-150--125</t>
         </is>
       </c>
       <c r="D297" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E297" s="2" t="inlineStr">
@@ -15349,7 +15349,7 @@
       <c r="K297" s="2" t="inlineStr"/>
       <c r="L297" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -15366,12 +15366,12 @@
       </c>
       <c r="C298" s="2" t="inlineStr">
         <is>
-          <t>11:-175--150</t>
+          <t>Ho:11:-175--150</t>
         </is>
       </c>
       <c r="D298" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E298" s="2" t="inlineStr">
@@ -15401,7 +15401,7 @@
       <c r="K298" s="2" t="inlineStr"/>
       <c r="L298" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -15418,12 +15418,12 @@
       </c>
       <c r="C299" s="2" t="inlineStr">
         <is>
-          <t>11:-200--175</t>
+          <t>Ho:11:-200--175</t>
         </is>
       </c>
       <c r="D299" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E299" s="2" t="inlineStr">
@@ -15453,7 +15453,7 @@
       <c r="K299" s="2" t="inlineStr"/>
       <c r="L299" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -15470,12 +15470,12 @@
       </c>
       <c r="C300" s="2" t="inlineStr">
         <is>
-          <t>11:-250--200</t>
+          <t>Ho:11:-250--200</t>
         </is>
       </c>
       <c r="D300" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E300" s="2" t="inlineStr">
@@ -15505,7 +15505,7 @@
       <c r="K300" s="2" t="inlineStr"/>
       <c r="L300" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -15522,12 +15522,12 @@
       </c>
       <c r="C301" s="2" t="inlineStr">
         <is>
-          <t>13:20-25</t>
+          <t>Hu:13:20-25</t>
         </is>
       </c>
       <c r="D301" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E301" s="2" t="inlineStr">
@@ -15557,7 +15557,7 @@
       <c r="K301" s="2" t="inlineStr"/>
       <c r="L301" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -15574,12 +15574,12 @@
       </c>
       <c r="C302" s="2" t="inlineStr">
         <is>
-          <t>13:10-20</t>
+          <t>Hu:13:10-20</t>
         </is>
       </c>
       <c r="D302" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E302" s="2" t="inlineStr">
@@ -15609,7 +15609,7 @@
       <c r="K302" s="2" t="inlineStr"/>
       <c r="L302" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -15626,12 +15626,12 @@
       </c>
       <c r="C303" s="2" t="inlineStr">
         <is>
-          <t>13:0-10</t>
+          <t>Hu:13:0-10</t>
         </is>
       </c>
       <c r="D303" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E303" s="2" t="inlineStr">
@@ -15661,7 +15661,7 @@
       <c r="K303" s="2" t="inlineStr"/>
       <c r="L303" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -15678,12 +15678,12 @@
       </c>
       <c r="C304" s="2" t="inlineStr">
         <is>
-          <t>13:-10-0</t>
+          <t>Hu:13:-10-0</t>
         </is>
       </c>
       <c r="D304" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E304" s="2" t="inlineStr">
@@ -15713,7 +15713,7 @@
       <c r="K304" s="2" t="inlineStr"/>
       <c r="L304" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -15730,12 +15730,12 @@
       </c>
       <c r="C305" s="2" t="inlineStr">
         <is>
-          <t>13:-10-0</t>
+          <t>Ho:13:-10-0</t>
         </is>
       </c>
       <c r="D305" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E305" s="2" t="inlineStr">
@@ -15765,7 +15765,7 @@
       <c r="K305" s="2" t="inlineStr"/>
       <c r="L305" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -15782,12 +15782,12 @@
       </c>
       <c r="C306" s="2" t="inlineStr">
         <is>
-          <t>13:-20--10</t>
+          <t>Ho:13:-20--10</t>
         </is>
       </c>
       <c r="D306" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E306" s="2" t="inlineStr">
@@ -15817,7 +15817,7 @@
       <c r="K306" s="2" t="inlineStr"/>
       <c r="L306" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -15834,12 +15834,12 @@
       </c>
       <c r="C307" s="2" t="inlineStr">
         <is>
-          <t>13:-30--20</t>
+          <t>Ho:13:-30--20</t>
         </is>
       </c>
       <c r="D307" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E307" s="2" t="inlineStr">
@@ -15869,7 +15869,7 @@
       <c r="K307" s="2" t="inlineStr"/>
       <c r="L307" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -15886,12 +15886,12 @@
       </c>
       <c r="C308" s="2" t="inlineStr">
         <is>
-          <t>13:-40--30</t>
+          <t>Ho:13:-40--30</t>
         </is>
       </c>
       <c r="D308" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E308" s="2" t="inlineStr">
@@ -15921,7 +15921,7 @@
       <c r="K308" s="2" t="inlineStr"/>
       <c r="L308" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -15938,12 +15938,12 @@
       </c>
       <c r="C309" s="2" t="inlineStr">
         <is>
-          <t>13:-50--40</t>
+          <t>Ho:13:-50--40</t>
         </is>
       </c>
       <c r="D309" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E309" s="2" t="inlineStr">
@@ -15973,7 +15973,7 @@
       <c r="K309" s="2" t="inlineStr"/>
       <c r="L309" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -15990,12 +15990,12 @@
       </c>
       <c r="C310" s="2" t="inlineStr">
         <is>
-          <t>13:-60--50</t>
+          <t>Ho:13:-60--50</t>
         </is>
       </c>
       <c r="D310" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E310" s="2" t="inlineStr">
@@ -16025,7 +16025,7 @@
       <c r="K310" s="2" t="inlineStr"/>
       <c r="L310" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -16042,12 +16042,12 @@
       </c>
       <c r="C311" s="2" t="inlineStr">
         <is>
-          <t>13:-70--60</t>
+          <t>Ho:13:-70--60</t>
         </is>
       </c>
       <c r="D311" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E311" s="2" t="inlineStr">
@@ -16077,7 +16077,7 @@
       <c r="K311" s="2" t="inlineStr"/>
       <c r="L311" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -16094,12 +16094,12 @@
       </c>
       <c r="C312" s="2" t="inlineStr">
         <is>
-          <t>13:-80--70</t>
+          <t>Ho:13:-80--70</t>
         </is>
       </c>
       <c r="D312" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E312" s="2" t="inlineStr">
@@ -16129,7 +16129,7 @@
       <c r="K312" s="2" t="inlineStr"/>
       <c r="L312" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -16146,12 +16146,12 @@
       </c>
       <c r="C313" s="2" t="inlineStr">
         <is>
-          <t>13:-90--80</t>
+          <t>Ho:13:-90--80</t>
         </is>
       </c>
       <c r="D313" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E313" s="2" t="inlineStr">
@@ -16181,7 +16181,7 @@
       <c r="K313" s="2" t="inlineStr"/>
       <c r="L313" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -16198,12 +16198,12 @@
       </c>
       <c r="C314" s="2" t="inlineStr">
         <is>
-          <t>13:-100--90</t>
+          <t>Ho:13:-100--90</t>
         </is>
       </c>
       <c r="D314" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E314" s="2" t="inlineStr">
@@ -16233,7 +16233,7 @@
       <c r="K314" s="2" t="inlineStr"/>
       <c r="L314" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -16250,12 +16250,12 @@
       </c>
       <c r="C315" s="2" t="inlineStr">
         <is>
-          <t>13:-125--100</t>
+          <t>Ho:13:-125--100</t>
         </is>
       </c>
       <c r="D315" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E315" s="2" t="inlineStr">
@@ -16285,7 +16285,7 @@
       <c r="K315" s="2" t="inlineStr"/>
       <c r="L315" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -16302,12 +16302,12 @@
       </c>
       <c r="C316" s="2" t="inlineStr">
         <is>
-          <t>13:-150--125</t>
+          <t>Ho:13:-150--125</t>
         </is>
       </c>
       <c r="D316" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E316" s="2" t="inlineStr">
@@ -16337,7 +16337,7 @@
       <c r="K316" s="2" t="inlineStr"/>
       <c r="L316" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -16354,12 +16354,12 @@
       </c>
       <c r="C317" s="2" t="inlineStr">
         <is>
-          <t>13:-175--150</t>
+          <t>Ho:13:-175--150</t>
         </is>
       </c>
       <c r="D317" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E317" s="2" t="inlineStr">
@@ -16389,7 +16389,7 @@
       <c r="K317" s="2" t="inlineStr"/>
       <c r="L317" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -16406,12 +16406,12 @@
       </c>
       <c r="C318" s="2" t="inlineStr">
         <is>
-          <t>13:-200--175</t>
+          <t>Ho:13:-200--175</t>
         </is>
       </c>
       <c r="D318" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E318" s="2" t="inlineStr">
@@ -16441,7 +16441,7 @@
       <c r="K318" s="2" t="inlineStr"/>
       <c r="L318" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -16458,12 +16458,12 @@
       </c>
       <c r="C319" s="2" t="inlineStr">
         <is>
-          <t>13:-250--200</t>
+          <t>Ho:13:-250--200</t>
         </is>
       </c>
       <c r="D319" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E319" s="2" t="inlineStr">
@@ -16493,7 +16493,7 @@
       <c r="K319" s="2" t="inlineStr"/>
       <c r="L319" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -16510,12 +16510,12 @@
       </c>
       <c r="C320" s="2" t="inlineStr">
         <is>
-          <t>13:-270--250</t>
+          <t>Ho:13:-270--250</t>
         </is>
       </c>
       <c r="D320" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E320" s="2" t="inlineStr">
@@ -16545,7 +16545,7 @@
       <c r="K320" s="2" t="inlineStr"/>
       <c r="L320" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -16562,12 +16562,12 @@
       </c>
       <c r="C321" s="2" t="inlineStr">
         <is>
-          <t>13:-300--270</t>
+          <t>Ho:13:-300--270</t>
         </is>
       </c>
       <c r="D321" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E321" s="2" t="inlineStr">
@@ -16597,7 +16597,7 @@
       <c r="K321" s="2" t="inlineStr"/>
       <c r="L321" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -16614,12 +16614,12 @@
       </c>
       <c r="C322" s="2" t="inlineStr">
         <is>
-          <t>14:0-10</t>
+          <t>Hu:14:0-10</t>
         </is>
       </c>
       <c r="D322" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E322" s="2" t="inlineStr">
@@ -16649,7 +16649,7 @@
       <c r="K322" s="2" t="inlineStr"/>
       <c r="L322" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -16666,12 +16666,12 @@
       </c>
       <c r="C323" s="2" t="inlineStr">
         <is>
-          <t>14:-10-0</t>
+          <t>Ho:14:-10-0</t>
         </is>
       </c>
       <c r="D323" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E323" s="2" t="inlineStr">
@@ -16701,7 +16701,7 @@
       <c r="K323" s="2" t="inlineStr"/>
       <c r="L323" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -16718,12 +16718,12 @@
       </c>
       <c r="C324" s="2" t="inlineStr">
         <is>
-          <t>14:-20--10</t>
+          <t>Ho:14:-20--10</t>
         </is>
       </c>
       <c r="D324" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E324" s="2" t="inlineStr">
@@ -16753,7 +16753,7 @@
       <c r="K324" s="2" t="inlineStr"/>
       <c r="L324" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -16770,12 +16770,12 @@
       </c>
       <c r="C325" s="2" t="inlineStr">
         <is>
-          <t>14:-30--20</t>
+          <t>Ho:14:-30--20</t>
         </is>
       </c>
       <c r="D325" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E325" s="2" t="inlineStr">
@@ -16805,7 +16805,7 @@
       <c r="K325" s="2" t="inlineStr"/>
       <c r="L325" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -16822,12 +16822,12 @@
       </c>
       <c r="C326" s="2" t="inlineStr">
         <is>
-          <t>14:-40--30</t>
+          <t>Ho:14:-40--30</t>
         </is>
       </c>
       <c r="D326" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E326" s="2" t="inlineStr">
@@ -16857,7 +16857,7 @@
       <c r="K326" s="2" t="inlineStr"/>
       <c r="L326" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -16874,12 +16874,12 @@
       </c>
       <c r="C327" s="2" t="inlineStr">
         <is>
-          <t>14:-50--40</t>
+          <t>Ho:14:-50--40</t>
         </is>
       </c>
       <c r="D327" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E327" s="2" t="inlineStr">
@@ -16909,7 +16909,7 @@
       <c r="K327" s="2" t="inlineStr"/>
       <c r="L327" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -16926,12 +16926,12 @@
       </c>
       <c r="C328" s="2" t="inlineStr">
         <is>
-          <t>14:-60--50</t>
+          <t>Ho:14:-60--50</t>
         </is>
       </c>
       <c r="D328" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E328" s="2" t="inlineStr">
@@ -16961,7 +16961,7 @@
       <c r="K328" s="2" t="inlineStr"/>
       <c r="L328" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -16978,12 +16978,12 @@
       </c>
       <c r="C329" s="2" t="inlineStr">
         <is>
-          <t>14:-70--60</t>
+          <t>Ho:14:-70--60</t>
         </is>
       </c>
       <c r="D329" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E329" s="2" t="inlineStr">
@@ -17013,7 +17013,7 @@
       <c r="K329" s="2" t="inlineStr"/>
       <c r="L329" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -17030,12 +17030,12 @@
       </c>
       <c r="C330" s="2" t="inlineStr">
         <is>
-          <t>14:-80--70</t>
+          <t>Ho:14:-80--70</t>
         </is>
       </c>
       <c r="D330" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E330" s="2" t="inlineStr">
@@ -17065,7 +17065,7 @@
       <c r="K330" s="2" t="inlineStr"/>
       <c r="L330" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -17082,12 +17082,12 @@
       </c>
       <c r="C331" s="2" t="inlineStr">
         <is>
-          <t>14:-90--80</t>
+          <t>Ho:14:-90--80</t>
         </is>
       </c>
       <c r="D331" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E331" s="2" t="inlineStr">
@@ -17117,7 +17117,7 @@
       <c r="K331" s="2" t="inlineStr"/>
       <c r="L331" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -17134,12 +17134,12 @@
       </c>
       <c r="C332" s="2" t="inlineStr">
         <is>
-          <t>14:-100--90</t>
+          <t>Ho:14:-100--90</t>
         </is>
       </c>
       <c r="D332" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E332" s="2" t="inlineStr">
@@ -17169,7 +17169,7 @@
       <c r="K332" s="2" t="inlineStr"/>
       <c r="L332" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -17186,12 +17186,12 @@
       </c>
       <c r="C333" s="2" t="inlineStr">
         <is>
-          <t>14:-125--100</t>
+          <t>Ho:14:-125--100</t>
         </is>
       </c>
       <c r="D333" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E333" s="2" t="inlineStr">
@@ -17221,7 +17221,7 @@
       <c r="K333" s="2" t="inlineStr"/>
       <c r="L333" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -17238,12 +17238,12 @@
       </c>
       <c r="C334" s="2" t="inlineStr">
         <is>
-          <t>14:-150--125</t>
+          <t>Ho:14:-150--125</t>
         </is>
       </c>
       <c r="D334" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E334" s="2" t="inlineStr">
@@ -17273,7 +17273,7 @@
       <c r="K334" s="2" t="inlineStr"/>
       <c r="L334" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -17290,12 +17290,12 @@
       </c>
       <c r="C335" s="2" t="inlineStr">
         <is>
-          <t>14:-175--150</t>
+          <t>Ho:14:-175--150</t>
         </is>
       </c>
       <c r="D335" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E335" s="2" t="inlineStr">
@@ -17325,7 +17325,7 @@
       <c r="K335" s="2" t="inlineStr"/>
       <c r="L335" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -17342,12 +17342,12 @@
       </c>
       <c r="C336" s="2" t="inlineStr">
         <is>
-          <t>14:-200--175</t>
+          <t>Ho:14:-200--175</t>
         </is>
       </c>
       <c r="D336" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E336" s="2" t="inlineStr">
@@ -17377,7 +17377,7 @@
       <c r="K336" s="2" t="inlineStr"/>
       <c r="L336" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -17394,12 +17394,12 @@
       </c>
       <c r="C337" s="2" t="inlineStr">
         <is>
-          <t>14:-215--200</t>
+          <t>Ho:14:-215--200</t>
         </is>
       </c>
       <c r="D337" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E337" s="2" t="inlineStr">
@@ -17429,7 +17429,7 @@
       <c r="K337" s="2" t="inlineStr"/>
       <c r="L337" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -17446,12 +17446,12 @@
       </c>
       <c r="C338" s="2" t="inlineStr">
         <is>
-          <t>14:-220--215</t>
+          <t>Ho:14:-220--215</t>
         </is>
       </c>
       <c r="D338" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E338" s="2" t="inlineStr">
@@ -17481,7 +17481,7 @@
       <c r="K338" s="2" t="inlineStr"/>
       <c r="L338" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -17498,12 +17498,12 @@
       </c>
       <c r="C339" s="2" t="inlineStr">
         <is>
-          <t>15:20-24</t>
+          <t>Hu:15:20-24</t>
         </is>
       </c>
       <c r="D339" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E339" s="2" t="inlineStr">
@@ -17533,7 +17533,7 @@
       <c r="K339" s="2" t="inlineStr"/>
       <c r="L339" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -17550,12 +17550,12 @@
       </c>
       <c r="C340" s="2" t="inlineStr">
         <is>
-          <t>15:10-20</t>
+          <t>Hu:15:10-20</t>
         </is>
       </c>
       <c r="D340" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E340" s="2" t="inlineStr">
@@ -17585,7 +17585,7 @@
       <c r="K340" s="2" t="inlineStr"/>
       <c r="L340" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -17602,12 +17602,12 @@
       </c>
       <c r="C341" s="2" t="inlineStr">
         <is>
-          <t>15:0-10</t>
+          <t>Hu:15:0-10</t>
         </is>
       </c>
       <c r="D341" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E341" s="2" t="inlineStr">
@@ -17637,7 +17637,7 @@
       <c r="K341" s="2" t="inlineStr"/>
       <c r="L341" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -17654,12 +17654,12 @@
       </c>
       <c r="C342" s="2" t="inlineStr">
         <is>
-          <t>15:-10-0</t>
+          <t>Hu:15:-10-0</t>
         </is>
       </c>
       <c r="D342" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E342" s="2" t="inlineStr">
@@ -17689,7 +17689,7 @@
       <c r="K342" s="2" t="inlineStr"/>
       <c r="L342" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -17706,12 +17706,12 @@
       </c>
       <c r="C343" s="2" t="inlineStr">
         <is>
-          <t>15:-10-0</t>
+          <t>Ho:15:-10-0</t>
         </is>
       </c>
       <c r="D343" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E343" s="2" t="inlineStr">
@@ -17741,7 +17741,7 @@
       <c r="K343" s="2" t="inlineStr"/>
       <c r="L343" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -17758,12 +17758,12 @@
       </c>
       <c r="C344" s="2" t="inlineStr">
         <is>
-          <t>15:-20--10</t>
+          <t>Ho:15:-20--10</t>
         </is>
       </c>
       <c r="D344" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E344" s="2" t="inlineStr">
@@ -17793,7 +17793,7 @@
       <c r="K344" s="2" t="inlineStr"/>
       <c r="L344" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -17810,12 +17810,12 @@
       </c>
       <c r="C345" s="2" t="inlineStr">
         <is>
-          <t>15:-30--20</t>
+          <t>Ho:15:-30--20</t>
         </is>
       </c>
       <c r="D345" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E345" s="2" t="inlineStr">
@@ -17845,7 +17845,7 @@
       <c r="K345" s="2" t="inlineStr"/>
       <c r="L345" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -17862,12 +17862,12 @@
       </c>
       <c r="C346" s="2" t="inlineStr">
         <is>
-          <t>15:-40--30</t>
+          <t>Ho:15:-40--30</t>
         </is>
       </c>
       <c r="D346" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E346" s="2" t="inlineStr">
@@ -17897,7 +17897,7 @@
       <c r="K346" s="2" t="inlineStr"/>
       <c r="L346" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -17914,12 +17914,12 @@
       </c>
       <c r="C347" s="2" t="inlineStr">
         <is>
-          <t>15:-50--40</t>
+          <t>Ho:15:-50--40</t>
         </is>
       </c>
       <c r="D347" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E347" s="2" t="inlineStr">
@@ -17949,7 +17949,7 @@
       <c r="K347" s="2" t="inlineStr"/>
       <c r="L347" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -17966,12 +17966,12 @@
       </c>
       <c r="C348" s="2" t="inlineStr">
         <is>
-          <t>15:-60--50</t>
+          <t>Ho:15:-60--50</t>
         </is>
       </c>
       <c r="D348" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E348" s="2" t="inlineStr">
@@ -18001,7 +18001,7 @@
       <c r="K348" s="2" t="inlineStr"/>
       <c r="L348" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -18018,12 +18018,12 @@
       </c>
       <c r="C349" s="2" t="inlineStr">
         <is>
-          <t>15:-70--60</t>
+          <t>Ho:15:-70--60</t>
         </is>
       </c>
       <c r="D349" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E349" s="2" t="inlineStr">
@@ -18053,7 +18053,7 @@
       <c r="K349" s="2" t="inlineStr"/>
       <c r="L349" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -18070,12 +18070,12 @@
       </c>
       <c r="C350" s="2" t="inlineStr">
         <is>
-          <t>15:-80--70</t>
+          <t>Ho:15:-80--70</t>
         </is>
       </c>
       <c r="D350" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E350" s="2" t="inlineStr">
@@ -18105,7 +18105,7 @@
       <c r="K350" s="2" t="inlineStr"/>
       <c r="L350" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -18122,12 +18122,12 @@
       </c>
       <c r="C351" s="2" t="inlineStr">
         <is>
-          <t>15:-90--80</t>
+          <t>Ho:15:-90--80</t>
         </is>
       </c>
       <c r="D351" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E351" s="2" t="inlineStr">
@@ -18157,7 +18157,7 @@
       <c r="K351" s="2" t="inlineStr"/>
       <c r="L351" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -18174,12 +18174,12 @@
       </c>
       <c r="C352" s="2" t="inlineStr">
         <is>
-          <t>15:-100--90</t>
+          <t>Ho:15:-100--90</t>
         </is>
       </c>
       <c r="D352" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E352" s="2" t="inlineStr">
@@ -18209,7 +18209,7 @@
       <c r="K352" s="2" t="inlineStr"/>
       <c r="L352" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -18226,12 +18226,12 @@
       </c>
       <c r="C353" s="2" t="inlineStr">
         <is>
-          <t>15:-125--100</t>
+          <t>Ho:15:-125--100</t>
         </is>
       </c>
       <c r="D353" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E353" s="2" t="inlineStr">
@@ -18261,7 +18261,7 @@
       <c r="K353" s="2" t="inlineStr"/>
       <c r="L353" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -18278,12 +18278,12 @@
       </c>
       <c r="C354" s="2" t="inlineStr">
         <is>
-          <t>15:-150--125</t>
+          <t>Ho:15:-150--125</t>
         </is>
       </c>
       <c r="D354" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E354" s="2" t="inlineStr">
@@ -18313,7 +18313,7 @@
       <c r="K354" s="2" t="inlineStr"/>
       <c r="L354" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -18330,12 +18330,12 @@
       </c>
       <c r="C355" s="2" t="inlineStr">
         <is>
-          <t>16:20-29</t>
+          <t>Hu:16:20-29</t>
         </is>
       </c>
       <c r="D355" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E355" s="2" t="inlineStr">
@@ -18365,7 +18365,7 @@
       <c r="K355" s="2" t="inlineStr"/>
       <c r="L355" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -18382,12 +18382,12 @@
       </c>
       <c r="C356" s="2" t="inlineStr">
         <is>
-          <t>16:10-20</t>
+          <t>Hu:16:10-20</t>
         </is>
       </c>
       <c r="D356" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E356" s="2" t="inlineStr">
@@ -18417,7 +18417,7 @@
       <c r="K356" s="2" t="inlineStr"/>
       <c r="L356" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -18434,12 +18434,12 @@
       </c>
       <c r="C357" s="2" t="inlineStr">
         <is>
-          <t>16:0-10</t>
+          <t>Hu:16:0-10</t>
         </is>
       </c>
       <c r="D357" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E357" s="2" t="inlineStr">
@@ -18469,7 +18469,7 @@
       <c r="K357" s="2" t="inlineStr"/>
       <c r="L357" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -18486,12 +18486,12 @@
       </c>
       <c r="C358" s="2" t="inlineStr">
         <is>
-          <t>16:-10-0</t>
+          <t>Hu:16:-10-0</t>
         </is>
       </c>
       <c r="D358" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E358" s="2" t="inlineStr">
@@ -18521,7 +18521,7 @@
       <c r="K358" s="2" t="inlineStr"/>
       <c r="L358" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -18538,12 +18538,12 @@
       </c>
       <c r="C359" s="2" t="inlineStr">
         <is>
-          <t>16:-10-0</t>
+          <t>Ho:16:-10-0</t>
         </is>
       </c>
       <c r="D359" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E359" s="2" t="inlineStr">
@@ -18573,7 +18573,7 @@
       <c r="K359" s="2" t="inlineStr"/>
       <c r="L359" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -18590,12 +18590,12 @@
       </c>
       <c r="C360" s="2" t="inlineStr">
         <is>
-          <t>16:-20--10</t>
+          <t>Ho:16:-20--10</t>
         </is>
       </c>
       <c r="D360" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E360" s="2" t="inlineStr">
@@ -18625,7 +18625,7 @@
       <c r="K360" s="2" t="inlineStr"/>
       <c r="L360" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -18642,12 +18642,12 @@
       </c>
       <c r="C361" s="2" t="inlineStr">
         <is>
-          <t>16:-30--20</t>
+          <t>Ho:16:-30--20</t>
         </is>
       </c>
       <c r="D361" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E361" s="2" t="inlineStr">
@@ -18677,7 +18677,7 @@
       <c r="K361" s="2" t="inlineStr"/>
       <c r="L361" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -18694,12 +18694,12 @@
       </c>
       <c r="C362" s="2" t="inlineStr">
         <is>
-          <t>16:-40--30</t>
+          <t>Ho:16:-40--30</t>
         </is>
       </c>
       <c r="D362" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E362" s="2" t="inlineStr">
@@ -18729,7 +18729,7 @@
       <c r="K362" s="2" t="inlineStr"/>
       <c r="L362" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -18746,12 +18746,12 @@
       </c>
       <c r="C363" s="2" t="inlineStr">
         <is>
-          <t>16:-50--40</t>
+          <t>Ho:16:-50--40</t>
         </is>
       </c>
       <c r="D363" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E363" s="2" t="inlineStr">
@@ -18781,7 +18781,7 @@
       <c r="K363" s="2" t="inlineStr"/>
       <c r="L363" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -18798,12 +18798,12 @@
       </c>
       <c r="C364" s="2" t="inlineStr">
         <is>
-          <t>16:-60--50</t>
+          <t>Ho:16:-60--50</t>
         </is>
       </c>
       <c r="D364" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E364" s="2" t="inlineStr">
@@ -18833,7 +18833,7 @@
       <c r="K364" s="2" t="inlineStr"/>
       <c r="L364" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -18850,12 +18850,12 @@
       </c>
       <c r="C365" s="2" t="inlineStr">
         <is>
-          <t>16:-70--60</t>
+          <t>Ho:16:-70--60</t>
         </is>
       </c>
       <c r="D365" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E365" s="2" t="inlineStr">
@@ -18885,7 +18885,7 @@
       <c r="K365" s="2" t="inlineStr"/>
       <c r="L365" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -18902,12 +18902,12 @@
       </c>
       <c r="C366" s="2" t="inlineStr">
         <is>
-          <t>16:-80--70</t>
+          <t>Ho:16:-80--70</t>
         </is>
       </c>
       <c r="D366" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E366" s="2" t="inlineStr">
@@ -18937,7 +18937,7 @@
       <c r="K366" s="2" t="inlineStr"/>
       <c r="L366" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -18954,12 +18954,12 @@
       </c>
       <c r="C367" s="2" t="inlineStr">
         <is>
-          <t>16:-90--80</t>
+          <t>Ho:16:-90--80</t>
         </is>
       </c>
       <c r="D367" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E367" s="2" t="inlineStr">
@@ -18989,7 +18989,7 @@
       <c r="K367" s="2" t="inlineStr"/>
       <c r="L367" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -19006,12 +19006,12 @@
       </c>
       <c r="C368" s="2" t="inlineStr">
         <is>
-          <t>16:-100--90</t>
+          <t>Ho:16:-100--90</t>
         </is>
       </c>
       <c r="D368" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E368" s="2" t="inlineStr">
@@ -19041,7 +19041,7 @@
       <c r="K368" s="2" t="inlineStr"/>
       <c r="L368" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -19058,12 +19058,12 @@
       </c>
       <c r="C369" s="2" t="inlineStr">
         <is>
-          <t>16:-125--100</t>
+          <t>Ho:16:-125--100</t>
         </is>
       </c>
       <c r="D369" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E369" s="2" t="inlineStr">
@@ -19093,7 +19093,7 @@
       <c r="K369" s="2" t="inlineStr"/>
       <c r="L369" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -19110,12 +19110,12 @@
       </c>
       <c r="C370" s="2" t="inlineStr">
         <is>
-          <t>16:-150--125</t>
+          <t>Ho:16:-150--125</t>
         </is>
       </c>
       <c r="D370" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E370" s="2" t="inlineStr">
@@ -19145,7 +19145,7 @@
       <c r="K370" s="2" t="inlineStr"/>
       <c r="L370" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -19162,12 +19162,12 @@
       </c>
       <c r="C371" s="2" t="inlineStr">
         <is>
-          <t>16:-175--150</t>
+          <t>Ho:16:-175--150</t>
         </is>
       </c>
       <c r="D371" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E371" s="2" t="inlineStr">
@@ -19197,7 +19197,7 @@
       <c r="K371" s="2" t="inlineStr"/>
       <c r="L371" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -19214,12 +19214,12 @@
       </c>
       <c r="C372" s="2" t="inlineStr">
         <is>
-          <t>16:-200--175</t>
+          <t>Ho:16:-200--175</t>
         </is>
       </c>
       <c r="D372" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E372" s="2" t="inlineStr">
@@ -19249,7 +19249,7 @@
       <c r="K372" s="2" t="inlineStr"/>
       <c r="L372" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -19266,12 +19266,12 @@
       </c>
       <c r="C373" s="2" t="inlineStr">
         <is>
-          <t>16:-250--200</t>
+          <t>Ho:16:-250--200</t>
         </is>
       </c>
       <c r="D373" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E373" s="2" t="inlineStr">
@@ -19301,7 +19301,7 @@
       <c r="K373" s="2" t="inlineStr"/>
       <c r="L373" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -19318,12 +19318,12 @@
       </c>
       <c r="C374" s="2" t="inlineStr">
         <is>
-          <t>17:20-25</t>
+          <t>Hu:17:20-25</t>
         </is>
       </c>
       <c r="D374" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E374" s="2" t="inlineStr">
@@ -19353,7 +19353,7 @@
       <c r="K374" s="2" t="inlineStr"/>
       <c r="L374" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -19370,12 +19370,12 @@
       </c>
       <c r="C375" s="2" t="inlineStr">
         <is>
-          <t>17:10-20</t>
+          <t>Hu:17:10-20</t>
         </is>
       </c>
       <c r="D375" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E375" s="2" t="inlineStr">
@@ -19405,7 +19405,7 @@
       <c r="K375" s="2" t="inlineStr"/>
       <c r="L375" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -19422,12 +19422,12 @@
       </c>
       <c r="C376" s="2" t="inlineStr">
         <is>
-          <t>17:0-10</t>
+          <t>Hu:17:0-10</t>
         </is>
       </c>
       <c r="D376" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E376" s="2" t="inlineStr">
@@ -19457,7 +19457,7 @@
       <c r="K376" s="2" t="inlineStr"/>
       <c r="L376" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -19474,12 +19474,12 @@
       </c>
       <c r="C377" s="2" t="inlineStr">
         <is>
-          <t>17:-10-0</t>
+          <t>Hu:17:-10-0</t>
         </is>
       </c>
       <c r="D377" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E377" s="2" t="inlineStr">
@@ -19509,7 +19509,7 @@
       <c r="K377" s="2" t="inlineStr"/>
       <c r="L377" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -19526,12 +19526,12 @@
       </c>
       <c r="C378" s="2" t="inlineStr">
         <is>
-          <t>17:-10-0</t>
+          <t>Ho:17:-10-0</t>
         </is>
       </c>
       <c r="D378" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E378" s="2" t="inlineStr">
@@ -19561,7 +19561,7 @@
       <c r="K378" s="2" t="inlineStr"/>
       <c r="L378" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -19578,12 +19578,12 @@
       </c>
       <c r="C379" s="2" t="inlineStr">
         <is>
-          <t>17:-20--10</t>
+          <t>Ho:17:-20--10</t>
         </is>
       </c>
       <c r="D379" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E379" s="2" t="inlineStr">
@@ -19613,7 +19613,7 @@
       <c r="K379" s="2" t="inlineStr"/>
       <c r="L379" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -19630,12 +19630,12 @@
       </c>
       <c r="C380" s="2" t="inlineStr">
         <is>
-          <t>17:-30--20</t>
+          <t>Ho:17:-30--20</t>
         </is>
       </c>
       <c r="D380" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E380" s="2" t="inlineStr">
@@ -19665,7 +19665,7 @@
       <c r="K380" s="2" t="inlineStr"/>
       <c r="L380" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -19682,12 +19682,12 @@
       </c>
       <c r="C381" s="2" t="inlineStr">
         <is>
-          <t>17:-40--30</t>
+          <t>Ho:17:-40--30</t>
         </is>
       </c>
       <c r="D381" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E381" s="2" t="inlineStr">
@@ -19717,7 +19717,7 @@
       <c r="K381" s="2" t="inlineStr"/>
       <c r="L381" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -19734,12 +19734,12 @@
       </c>
       <c r="C382" s="2" t="inlineStr">
         <is>
-          <t>17:-50--40</t>
+          <t>Ho:17:-50--40</t>
         </is>
       </c>
       <c r="D382" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E382" s="2" t="inlineStr">
@@ -19769,7 +19769,7 @@
       <c r="K382" s="2" t="inlineStr"/>
       <c r="L382" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -19786,12 +19786,12 @@
       </c>
       <c r="C383" s="2" t="inlineStr">
         <is>
-          <t>17:-60--50</t>
+          <t>Ho:17:-60--50</t>
         </is>
       </c>
       <c r="D383" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E383" s="2" t="inlineStr">
@@ -19821,7 +19821,7 @@
       <c r="K383" s="2" t="inlineStr"/>
       <c r="L383" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -19838,12 +19838,12 @@
       </c>
       <c r="C384" s="2" t="inlineStr">
         <is>
-          <t>17:-70--60</t>
+          <t>Ho:17:-70--60</t>
         </is>
       </c>
       <c r="D384" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E384" s="2" t="inlineStr">
@@ -19873,7 +19873,7 @@
       <c r="K384" s="2" t="inlineStr"/>
       <c r="L384" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -19890,12 +19890,12 @@
       </c>
       <c r="C385" s="2" t="inlineStr">
         <is>
-          <t>17:-80--70</t>
+          <t>Ho:17:-80--70</t>
         </is>
       </c>
       <c r="D385" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E385" s="2" t="inlineStr">
@@ -19925,7 +19925,7 @@
       <c r="K385" s="2" t="inlineStr"/>
       <c r="L385" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -19942,12 +19942,12 @@
       </c>
       <c r="C386" s="2" t="inlineStr">
         <is>
-          <t>17:-90--80</t>
+          <t>Ho:17:-90--80</t>
         </is>
       </c>
       <c r="D386" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E386" s="2" t="inlineStr">
@@ -19977,7 +19977,7 @@
       <c r="K386" s="2" t="inlineStr"/>
       <c r="L386" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -19994,12 +19994,12 @@
       </c>
       <c r="C387" s="2" t="inlineStr">
         <is>
-          <t>17:-100--90</t>
+          <t>Ho:17:-100--90</t>
         </is>
       </c>
       <c r="D387" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E387" s="2" t="inlineStr">
@@ -20029,7 +20029,7 @@
       <c r="K387" s="2" t="inlineStr"/>
       <c r="L387" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -20046,12 +20046,12 @@
       </c>
       <c r="C388" s="2" t="inlineStr">
         <is>
-          <t>17:-125--100</t>
+          <t>Ho:17:-125--100</t>
         </is>
       </c>
       <c r="D388" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E388" s="2" t="inlineStr">
@@ -20081,7 +20081,7 @@
       <c r="K388" s="2" t="inlineStr"/>
       <c r="L388" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -20098,12 +20098,12 @@
       </c>
       <c r="C389" s="2" t="inlineStr">
         <is>
-          <t>17:-150--125</t>
+          <t>Ho:17:-150--125</t>
         </is>
       </c>
       <c r="D389" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E389" s="2" t="inlineStr">
@@ -20133,7 +20133,7 @@
       <c r="K389" s="2" t="inlineStr"/>
       <c r="L389" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -20150,12 +20150,12 @@
       </c>
       <c r="C390" s="2" t="inlineStr">
         <is>
-          <t>17:-175--150</t>
+          <t>Ho:17:-175--150</t>
         </is>
       </c>
       <c r="D390" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E390" s="2" t="inlineStr">
@@ -20185,7 +20185,7 @@
       <c r="K390" s="2" t="inlineStr"/>
       <c r="L390" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -20202,12 +20202,12 @@
       </c>
       <c r="C391" s="2" t="inlineStr">
         <is>
-          <t>17:-200--175</t>
+          <t>Ho:17:-200--175</t>
         </is>
       </c>
       <c r="D391" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E391" s="2" t="inlineStr">
@@ -20237,7 +20237,7 @@
       <c r="K391" s="2" t="inlineStr"/>
       <c r="L391" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -20254,12 +20254,12 @@
       </c>
       <c r="C392" s="2" t="inlineStr">
         <is>
-          <t>17:-239--200</t>
+          <t>Ho:17:-239--200</t>
         </is>
       </c>
       <c r="D392" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E392" s="2" t="inlineStr">
@@ -20289,7 +20289,7 @@
       <c r="K392" s="2" t="inlineStr"/>
       <c r="L392" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -20306,12 +20306,12 @@
       </c>
       <c r="C393" s="2" t="inlineStr">
         <is>
-          <t>19:10-20</t>
+          <t>Hu:19:10-20</t>
         </is>
       </c>
       <c r="D393" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E393" s="2" t="inlineStr">
@@ -20341,7 +20341,7 @@
       <c r="K393" s="2" t="inlineStr"/>
       <c r="L393" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -20358,12 +20358,12 @@
       </c>
       <c r="C394" s="2" t="inlineStr">
         <is>
-          <t>19:0-10</t>
+          <t>Hu:19:0-10</t>
         </is>
       </c>
       <c r="D394" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E394" s="2" t="inlineStr">
@@ -20393,7 +20393,7 @@
       <c r="K394" s="2" t="inlineStr"/>
       <c r="L394" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -20410,12 +20410,12 @@
       </c>
       <c r="C395" s="2" t="inlineStr">
         <is>
-          <t>19:-10-0</t>
+          <t>Ho:19:-10-0</t>
         </is>
       </c>
       <c r="D395" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E395" s="2" t="inlineStr">
@@ -20445,7 +20445,7 @@
       <c r="K395" s="2" t="inlineStr"/>
       <c r="L395" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -20462,12 +20462,12 @@
       </c>
       <c r="C396" s="2" t="inlineStr">
         <is>
-          <t>19:-20--10</t>
+          <t>Ho:19:-20--10</t>
         </is>
       </c>
       <c r="D396" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E396" s="2" t="inlineStr">
@@ -20497,7 +20497,7 @@
       <c r="K396" s="2" t="inlineStr"/>
       <c r="L396" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -20514,12 +20514,12 @@
       </c>
       <c r="C397" s="2" t="inlineStr">
         <is>
-          <t>19:-30--20</t>
+          <t>Ho:19:-30--20</t>
         </is>
       </c>
       <c r="D397" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E397" s="2" t="inlineStr">
@@ -20549,7 +20549,7 @@
       <c r="K397" s="2" t="inlineStr"/>
       <c r="L397" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -20566,12 +20566,12 @@
       </c>
       <c r="C398" s="2" t="inlineStr">
         <is>
-          <t>19:-40--30</t>
+          <t>Ho:19:-40--30</t>
         </is>
       </c>
       <c r="D398" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E398" s="2" t="inlineStr">
@@ -20601,7 +20601,7 @@
       <c r="K398" s="2" t="inlineStr"/>
       <c r="L398" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -20618,12 +20618,12 @@
       </c>
       <c r="C399" s="2" t="inlineStr">
         <is>
-          <t>19:-50--40</t>
+          <t>Ho:19:-50--40</t>
         </is>
       </c>
       <c r="D399" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E399" s="2" t="inlineStr">
@@ -20653,7 +20653,7 @@
       <c r="K399" s="2" t="inlineStr"/>
       <c r="L399" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -20670,12 +20670,12 @@
       </c>
       <c r="C400" s="2" t="inlineStr">
         <is>
-          <t>19:-60--50</t>
+          <t>Ho:19:-60--50</t>
         </is>
       </c>
       <c r="D400" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E400" s="2" t="inlineStr">
@@ -20705,7 +20705,7 @@
       <c r="K400" s="2" t="inlineStr"/>
       <c r="L400" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -20722,12 +20722,12 @@
       </c>
       <c r="C401" s="2" t="inlineStr">
         <is>
-          <t>19:-70--60</t>
+          <t>Ho:19:-70--60</t>
         </is>
       </c>
       <c r="D401" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E401" s="2" t="inlineStr">
@@ -20757,7 +20757,7 @@
       <c r="K401" s="2" t="inlineStr"/>
       <c r="L401" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -20774,12 +20774,12 @@
       </c>
       <c r="C402" s="2" t="inlineStr">
         <is>
-          <t>19:-80--70</t>
+          <t>Ho:19:-80--70</t>
         </is>
       </c>
       <c r="D402" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E402" s="2" t="inlineStr">
@@ -20809,7 +20809,7 @@
       <c r="K402" s="2" t="inlineStr"/>
       <c r="L402" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -20826,12 +20826,12 @@
       </c>
       <c r="C403" s="2" t="inlineStr">
         <is>
-          <t>19:-90--80</t>
+          <t>Ho:19:-90--80</t>
         </is>
       </c>
       <c r="D403" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E403" s="2" t="inlineStr">
@@ -20861,7 +20861,7 @@
       <c r="K403" s="2" t="inlineStr"/>
       <c r="L403" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -20878,12 +20878,12 @@
       </c>
       <c r="C404" s="2" t="inlineStr">
         <is>
-          <t>19:-100--90</t>
+          <t>Ho:19:-100--90</t>
         </is>
       </c>
       <c r="D404" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E404" s="2" t="inlineStr">
@@ -20913,7 +20913,7 @@
       <c r="K404" s="2" t="inlineStr"/>
       <c r="L404" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -20930,12 +20930,12 @@
       </c>
       <c r="C405" s="2" t="inlineStr">
         <is>
-          <t>19:-125--100</t>
+          <t>Ho:19:-125--100</t>
         </is>
       </c>
       <c r="D405" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E405" s="2" t="inlineStr">
@@ -20965,7 +20965,7 @@
       <c r="K405" s="2" t="inlineStr"/>
       <c r="L405" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -20982,12 +20982,12 @@
       </c>
       <c r="C406" s="2" t="inlineStr">
         <is>
-          <t>19:-150--125</t>
+          <t>Ho:19:-150--125</t>
         </is>
       </c>
       <c r="D406" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E406" s="2" t="inlineStr">
@@ -21017,7 +21017,7 @@
       <c r="K406" s="2" t="inlineStr"/>
       <c r="L406" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -21034,12 +21034,12 @@
       </c>
       <c r="C407" s="2" t="inlineStr">
         <is>
-          <t>19:-175--150</t>
+          <t>Ho:19:-175--150</t>
         </is>
       </c>
       <c r="D407" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E407" s="2" t="inlineStr">
@@ -21069,7 +21069,7 @@
       <c r="K407" s="2" t="inlineStr"/>
       <c r="L407" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -21086,12 +21086,12 @@
       </c>
       <c r="C408" s="2" t="inlineStr">
         <is>
-          <t>19:-200--175</t>
+          <t>Ho:19:-200--175</t>
         </is>
       </c>
       <c r="D408" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E408" s="2" t="inlineStr">
@@ -21121,7 +21121,7 @@
       <c r="K408" s="2" t="inlineStr"/>
       <c r="L408" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -21138,12 +21138,12 @@
       </c>
       <c r="C409" s="2" t="inlineStr">
         <is>
-          <t>19:-216--200</t>
+          <t>Ho:19:-216--200</t>
         </is>
       </c>
       <c r="D409" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E409" s="2" t="inlineStr">
@@ -21173,7 +21173,7 @@
       <c r="K409" s="2" t="inlineStr"/>
       <c r="L409" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -21190,12 +21190,12 @@
       </c>
       <c r="C410" s="2" t="inlineStr">
         <is>
-          <t>19:-250--216</t>
+          <t>Ho:19:-250--216</t>
         </is>
       </c>
       <c r="D410" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E410" s="2" t="inlineStr">
@@ -21225,7 +21225,7 @@
       <c r="K410" s="2" t="inlineStr"/>
       <c r="L410" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -21242,12 +21242,12 @@
       </c>
       <c r="C411" s="2" t="inlineStr">
         <is>
-          <t>20:10-19</t>
+          <t>Hu:20:10-19</t>
         </is>
       </c>
       <c r="D411" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E411" s="2" t="inlineStr">
@@ -21277,7 +21277,7 @@
       <c r="K411" s="2" t="inlineStr"/>
       <c r="L411" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -21294,12 +21294,12 @@
       </c>
       <c r="C412" s="2" t="inlineStr">
         <is>
-          <t>20:0-10</t>
+          <t>Hu:20:0-10</t>
         </is>
       </c>
       <c r="D412" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E412" s="2" t="inlineStr">
@@ -21329,7 +21329,7 @@
       <c r="K412" s="2" t="inlineStr"/>
       <c r="L412" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -21346,12 +21346,12 @@
       </c>
       <c r="C413" s="2" t="inlineStr">
         <is>
-          <t>20:-10-0</t>
+          <t>Hu:20:-10-0</t>
         </is>
       </c>
       <c r="D413" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E413" s="2" t="inlineStr">
@@ -21381,7 +21381,7 @@
       <c r="K413" s="2" t="inlineStr"/>
       <c r="L413" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -21398,12 +21398,12 @@
       </c>
       <c r="C414" s="2" t="inlineStr">
         <is>
-          <t>20:-10-0</t>
+          <t>Ho:20:-10-0</t>
         </is>
       </c>
       <c r="D414" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E414" s="2" t="inlineStr">
@@ -21433,7 +21433,7 @@
       <c r="K414" s="2" t="inlineStr"/>
       <c r="L414" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -21450,12 +21450,12 @@
       </c>
       <c r="C415" s="2" t="inlineStr">
         <is>
-          <t>20:-20--10</t>
+          <t>Ho:20:-20--10</t>
         </is>
       </c>
       <c r="D415" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E415" s="2" t="inlineStr">
@@ -21485,7 +21485,7 @@
       <c r="K415" s="2" t="inlineStr"/>
       <c r="L415" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -21502,12 +21502,12 @@
       </c>
       <c r="C416" s="2" t="inlineStr">
         <is>
-          <t>20:-30--20</t>
+          <t>Ho:20:-30--20</t>
         </is>
       </c>
       <c r="D416" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E416" s="2" t="inlineStr">
@@ -21537,7 +21537,7 @@
       <c r="K416" s="2" t="inlineStr"/>
       <c r="L416" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -21554,12 +21554,12 @@
       </c>
       <c r="C417" s="2" t="inlineStr">
         <is>
-          <t>20:-40--30</t>
+          <t>Ho:20:-40--30</t>
         </is>
       </c>
       <c r="D417" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E417" s="2" t="inlineStr">
@@ -21589,7 +21589,7 @@
       <c r="K417" s="2" t="inlineStr"/>
       <c r="L417" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -21606,12 +21606,12 @@
       </c>
       <c r="C418" s="2" t="inlineStr">
         <is>
-          <t>20:-50--40</t>
+          <t>Ho:20:-50--40</t>
         </is>
       </c>
       <c r="D418" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E418" s="2" t="inlineStr">
@@ -21641,7 +21641,7 @@
       <c r="K418" s="2" t="inlineStr"/>
       <c r="L418" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -21658,12 +21658,12 @@
       </c>
       <c r="C419" s="2" t="inlineStr">
         <is>
-          <t>20:-60--50</t>
+          <t>Ho:20:-60--50</t>
         </is>
       </c>
       <c r="D419" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E419" s="2" t="inlineStr">
@@ -21693,7 +21693,7 @@
       <c r="K419" s="2" t="inlineStr"/>
       <c r="L419" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -21710,12 +21710,12 @@
       </c>
       <c r="C420" s="2" t="inlineStr">
         <is>
-          <t>20:-70--60</t>
+          <t>Ho:20:-70--60</t>
         </is>
       </c>
       <c r="D420" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E420" s="2" t="inlineStr">
@@ -21745,7 +21745,7 @@
       <c r="K420" s="2" t="inlineStr"/>
       <c r="L420" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -21762,12 +21762,12 @@
       </c>
       <c r="C421" s="2" t="inlineStr">
         <is>
-          <t>20:-80--70</t>
+          <t>Ho:20:-80--70</t>
         </is>
       </c>
       <c r="D421" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E421" s="2" t="inlineStr">
@@ -21797,7 +21797,7 @@
       <c r="K421" s="2" t="inlineStr"/>
       <c r="L421" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -21814,12 +21814,12 @@
       </c>
       <c r="C422" s="2" t="inlineStr">
         <is>
-          <t>20:-90--80</t>
+          <t>Ho:20:-90--80</t>
         </is>
       </c>
       <c r="D422" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E422" s="2" t="inlineStr">
@@ -21849,7 +21849,7 @@
       <c r="K422" s="2" t="inlineStr"/>
       <c r="L422" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -21866,12 +21866,12 @@
       </c>
       <c r="C423" s="2" t="inlineStr">
         <is>
-          <t>20:-100--90</t>
+          <t>Ho:20:-100--90</t>
         </is>
       </c>
       <c r="D423" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E423" s="2" t="inlineStr">
@@ -21901,7 +21901,7 @@
       <c r="K423" s="2" t="inlineStr"/>
       <c r="L423" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -21918,12 +21918,12 @@
       </c>
       <c r="C424" s="2" t="inlineStr">
         <is>
-          <t>20:-125--100</t>
+          <t>Ho:20:-125--100</t>
         </is>
       </c>
       <c r="D424" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E424" s="2" t="inlineStr">
@@ -21953,7 +21953,7 @@
       <c r="K424" s="2" t="inlineStr"/>
       <c r="L424" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -21970,12 +21970,12 @@
       </c>
       <c r="C425" s="2" t="inlineStr">
         <is>
-          <t>20:-150--125</t>
+          <t>Ho:20:-150--125</t>
         </is>
       </c>
       <c r="D425" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E425" s="2" t="inlineStr">
@@ -22005,7 +22005,7 @@
       <c r="K425" s="2" t="inlineStr"/>
       <c r="L425" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -22022,12 +22022,12 @@
       </c>
       <c r="C426" s="2" t="inlineStr">
         <is>
-          <t>20:-175--150</t>
+          <t>Ho:20:-175--150</t>
         </is>
       </c>
       <c r="D426" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E426" s="2" t="inlineStr">
@@ -22057,7 +22057,7 @@
       <c r="K426" s="2" t="inlineStr"/>
       <c r="L426" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -22074,12 +22074,12 @@
       </c>
       <c r="C427" s="2" t="inlineStr">
         <is>
-          <t>20:-200--175</t>
+          <t>Ho:20:-200--175</t>
         </is>
       </c>
       <c r="D427" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E427" s="2" t="inlineStr">
@@ -22109,7 +22109,7 @@
       <c r="K427" s="2" t="inlineStr"/>
       <c r="L427" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -22126,12 +22126,12 @@
       </c>
       <c r="C428" s="2" t="inlineStr">
         <is>
-          <t>20:-250--200</t>
+          <t>Ho:20:-250--200</t>
         </is>
       </c>
       <c r="D428" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E428" s="2" t="inlineStr">
@@ -22161,7 +22161,7 @@
       <c r="K428" s="2" t="inlineStr"/>
       <c r="L428" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -22178,12 +22178,12 @@
       </c>
       <c r="C429" s="2" t="inlineStr">
         <is>
-          <t>20:-300--250</t>
+          <t>Ho:20:-300--250</t>
         </is>
       </c>
       <c r="D429" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E429" s="2" t="inlineStr">
@@ -22213,7 +22213,7 @@
       <c r="K429" s="2" t="inlineStr"/>
       <c r="L429" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -22230,12 +22230,12 @@
       </c>
       <c r="C430" s="2" t="inlineStr">
         <is>
-          <t>21:10-20</t>
+          <t>Hu:21:10-20</t>
         </is>
       </c>
       <c r="D430" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E430" s="2" t="inlineStr">
@@ -22265,7 +22265,7 @@
       <c r="K430" s="2" t="inlineStr"/>
       <c r="L430" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -22282,12 +22282,12 @@
       </c>
       <c r="C431" s="2" t="inlineStr">
         <is>
-          <t>21:0-10</t>
+          <t>Hu:21:0-10</t>
         </is>
       </c>
       <c r="D431" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E431" s="2" t="inlineStr">
@@ -22317,7 +22317,7 @@
       <c r="K431" s="2" t="inlineStr"/>
       <c r="L431" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -22334,12 +22334,12 @@
       </c>
       <c r="C432" s="2" t="inlineStr">
         <is>
-          <t>21:-10-0</t>
+          <t>Ho:21:-10-0</t>
         </is>
       </c>
       <c r="D432" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E432" s="2" t="inlineStr">
@@ -22369,7 +22369,7 @@
       <c r="K432" s="2" t="inlineStr"/>
       <c r="L432" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -22386,12 +22386,12 @@
       </c>
       <c r="C433" s="2" t="inlineStr">
         <is>
-          <t>21:-20--10</t>
+          <t>Ho:21:-20--10</t>
         </is>
       </c>
       <c r="D433" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E433" s="2" t="inlineStr">
@@ -22421,7 +22421,7 @@
       <c r="K433" s="2" t="inlineStr"/>
       <c r="L433" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -22438,12 +22438,12 @@
       </c>
       <c r="C434" s="2" t="inlineStr">
         <is>
-          <t>21:-30--20</t>
+          <t>Ho:21:-30--20</t>
         </is>
       </c>
       <c r="D434" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E434" s="2" t="inlineStr">
@@ -22473,7 +22473,7 @@
       <c r="K434" s="2" t="inlineStr"/>
       <c r="L434" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -22490,12 +22490,12 @@
       </c>
       <c r="C435" s="2" t="inlineStr">
         <is>
-          <t>21:-40--30</t>
+          <t>Ho:21:-40--30</t>
         </is>
       </c>
       <c r="D435" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E435" s="2" t="inlineStr">
@@ -22525,7 +22525,7 @@
       <c r="K435" s="2" t="inlineStr"/>
       <c r="L435" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -22542,12 +22542,12 @@
       </c>
       <c r="C436" s="2" t="inlineStr">
         <is>
-          <t>21:-50--40</t>
+          <t>Ho:21:-50--40</t>
         </is>
       </c>
       <c r="D436" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E436" s="2" t="inlineStr">
@@ -22577,7 +22577,7 @@
       <c r="K436" s="2" t="inlineStr"/>
       <c r="L436" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -22594,12 +22594,12 @@
       </c>
       <c r="C437" s="2" t="inlineStr">
         <is>
-          <t>21:-60--50</t>
+          <t>Ho:21:-60--50</t>
         </is>
       </c>
       <c r="D437" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E437" s="2" t="inlineStr">
@@ -22629,7 +22629,7 @@
       <c r="K437" s="2" t="inlineStr"/>
       <c r="L437" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -22646,12 +22646,12 @@
       </c>
       <c r="C438" s="2" t="inlineStr">
         <is>
-          <t>21:-70--60</t>
+          <t>Ho:21:-70--60</t>
         </is>
       </c>
       <c r="D438" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E438" s="2" t="inlineStr">
@@ -22681,7 +22681,7 @@
       <c r="K438" s="2" t="inlineStr"/>
       <c r="L438" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -22698,12 +22698,12 @@
       </c>
       <c r="C439" s="2" t="inlineStr">
         <is>
-          <t>21:-80--70</t>
+          <t>Ho:21:-80--70</t>
         </is>
       </c>
       <c r="D439" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E439" s="2" t="inlineStr">
@@ -22733,7 +22733,7 @@
       <c r="K439" s="2" t="inlineStr"/>
       <c r="L439" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -22750,12 +22750,12 @@
       </c>
       <c r="C440" s="2" t="inlineStr">
         <is>
-          <t>21:-90--80</t>
+          <t>Ho:21:-90--80</t>
         </is>
       </c>
       <c r="D440" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E440" s="2" t="inlineStr">
@@ -22785,7 +22785,7 @@
       <c r="K440" s="2" t="inlineStr"/>
       <c r="L440" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -22802,12 +22802,12 @@
       </c>
       <c r="C441" s="2" t="inlineStr">
         <is>
-          <t>21:-100--90</t>
+          <t>Ho:21:-100--90</t>
         </is>
       </c>
       <c r="D441" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E441" s="2" t="inlineStr">
@@ -22837,7 +22837,7 @@
       <c r="K441" s="2" t="inlineStr"/>
       <c r="L441" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -22854,12 +22854,12 @@
       </c>
       <c r="C442" s="2" t="inlineStr">
         <is>
-          <t>21:-125--100</t>
+          <t>Ho:21:-125--100</t>
         </is>
       </c>
       <c r="D442" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E442" s="2" t="inlineStr">
@@ -22889,7 +22889,7 @@
       <c r="K442" s="2" t="inlineStr"/>
       <c r="L442" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -22906,12 +22906,12 @@
       </c>
       <c r="C443" s="2" t="inlineStr">
         <is>
-          <t>21:-150--125</t>
+          <t>Ho:21:-150--125</t>
         </is>
       </c>
       <c r="D443" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E443" s="2" t="inlineStr">
@@ -22941,7 +22941,7 @@
       <c r="K443" s="2" t="inlineStr"/>
       <c r="L443" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -22958,12 +22958,12 @@
       </c>
       <c r="C444" s="2" t="inlineStr">
         <is>
-          <t>21:-175--150</t>
+          <t>Ho:21:-175--150</t>
         </is>
       </c>
       <c r="D444" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E444" s="2" t="inlineStr">
@@ -22993,7 +22993,7 @@
       <c r="K444" s="2" t="inlineStr"/>
       <c r="L444" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -23010,12 +23010,12 @@
       </c>
       <c r="C445" s="2" t="inlineStr">
         <is>
-          <t>21:-200--175</t>
+          <t>Ho:21:-200--175</t>
         </is>
       </c>
       <c r="D445" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E445" s="2" t="inlineStr">
@@ -23045,7 +23045,7 @@
       <c r="K445" s="2" t="inlineStr"/>
       <c r="L445" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -23062,12 +23062,12 @@
       </c>
       <c r="C446" s="2" t="inlineStr">
         <is>
-          <t>21:-250--200</t>
+          <t>Ho:21:-250--200</t>
         </is>
       </c>
       <c r="D446" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E446" s="2" t="inlineStr">
@@ -23097,7 +23097,7 @@
       <c r="K446" s="2" t="inlineStr"/>
       <c r="L446" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Al (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
